--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{419ED2A4-D047-489E-A604-D64B4214EA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{439BD3B3-8C9A-4053-BA1C-0A17AA823FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="222">
   <si>
     <t>No</t>
   </si>
@@ -65,12 +65,30 @@
     <t>Imagen</t>
   </si>
   <si>
+    <t>Visible</t>
+  </si>
+  <si>
+    <t>Disponible</t>
+  </si>
+  <si>
+    <t>Destacado</t>
+  </si>
+  <si>
+    <t>Orden</t>
+  </si>
+  <si>
     <t>Tortilla Carne de Zafiro</t>
   </si>
   <si>
     <t>Tortilla rellena de queso fundiddo ° Carne desmechada y aguacate con ahogao</t>
   </si>
   <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
     <t>Corn Dog Zafiro Bites</t>
   </si>
   <si>
@@ -185,7 +203,13 @@
     <t>Pan tajado crujiente, con base de nnutella, fresas, arandanos, melocoton y menta fresca.</t>
   </si>
   <si>
+    <t> </t>
+  </si>
+  <si>
     <t>Margaritas </t>
+  </si>
+  <si>
+    <t>Tequila, cítricos y licor de naranja en una mezcla fresca y vibrante, con borde escarchado y carácter clásico.</t>
   </si>
   <si>
     <t>Con alcohol</t>
@@ -202,10 +226,13 @@
     <t xml:space="preserve">Copa Margarita                                                  </t>
   </si>
   <si>
-    <t>images/menu/alcohol/01-margaritas-surtidas.png</t>
+    <t>images/menu/alcohol/01-margaritas-surtidas.jpeg</t>
   </si>
   <si>
     <t>Coctel Tequila Sunrise </t>
+  </si>
+  <si>
+    <t>Tequila, naranja y granadina en una mezcla frutal y colorida, ideal para un perfil fresco y dulce al atardecer.</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 Oz  A 2 Oz De Tequila Reposado. 
@@ -226,6 +253,9 @@
     <t>Coctel Orgasmo</t>
   </si>
   <si>
+    <t>Licor de café, amaretto y crema de whisky en una mezcla suave, cremosa y de perfil dulce.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 Oz Licor De Café 
 1 Oz Licor De Amaretto 
 2 Oz Licor De Crema De Beilys  
@@ -243,6 +273,9 @@
     <t>Cuba Libre </t>
   </si>
   <si>
+    <t>Ron, Coca-Cola y limón en un clásico refrescante, con un toque cítrico y fácil de disfrutar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ron Bacardi Añejo O Ron Viejo Del Caldas. 
 1 Oz (Jugo De Medio Limón. 
 4 Oz Refresco De Coca-Cola. 
@@ -254,10 +287,13 @@
     <t>Old Fashion</t>
   </si>
   <si>
-    <t>images/menu/alcohol/04-cuba-libre.jpg</t>
+    <t>images/menu/alcohol/04-cuba-libre.jpeg</t>
   </si>
   <si>
     <t>Mojito</t>
+  </si>
+  <si>
+    <t>Ron blanco, limón, hierbabuena y soda en una mezcla refrescante, herbal y muy ligera.</t>
   </si>
   <si>
     <t xml:space="preserve">2 Oz De Ron Blanco Carta Blanca. 
@@ -271,10 +307,13 @@
     <t>Copa Alta</t>
   </si>
   <si>
-    <t>images/menu/alcohol/05-mojito.jpg</t>
+    <t>images/menu/alcohol/05-mojito.jpeg</t>
   </si>
   <si>
     <t>El Padrino  </t>
+  </si>
+  <si>
+    <t>Whisky y amaretto en una combinación corta, elegante y de perfil cálido con notas dulces.</t>
   </si>
   <si>
     <t>2 O 3 Oz  De Whisky Escocés (Opcional). 
@@ -291,6 +330,9 @@
   </si>
   <si>
     <t>Piña Colada  </t>
+  </si>
+  <si>
+    <t>Ron, coco y piña en una mezcla cremosa, tropical y suave.</t>
   </si>
   <si>
     <t xml:space="preserve">2 Oz  De Ron Blanco Carta Blanca. 
@@ -311,6 +353,9 @@
     <t>Gin-Tonic </t>
   </si>
   <si>
+    <t>Ginebra y tónica en una mezcla fresca y limpia, con notas botánicas y cítricas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 Oz Ginebra (Preferiblemente Tipo London Dry Beefeater). 
 Agua Tónica: 100-150 Ml (Bien Fría). 
 Hielo: Cubitos Pequeños Y Compactos. 
@@ -321,10 +366,13 @@
     <t>Copa balon</t>
   </si>
   <si>
-    <t>images/menu/alcohol/08-gin-tonic.png</t>
+    <t>images/menu/alcohol/08-gin-tonic.jpeg</t>
   </si>
   <si>
     <t>Dry Martini </t>
+  </si>
+  <si>
+    <t>Ginebra y vermut seco en una copa clásica, limpia y elegante.</t>
   </si>
   <si>
     <t xml:space="preserve">2 Oz De Ginebra London Dry Beefeater. 
@@ -336,10 +384,13 @@
     <t>Copa Martini</t>
   </si>
   <si>
-    <t>images/menu/alcohol/09-dry-martini.jpg</t>
+    <t>images/menu/alcohol/09-dry-martini.jpeg</t>
   </si>
   <si>
     <t>Passion Fresh</t>
+  </si>
+  <si>
+    <t>Ron, vodka y notas frutales de sandía y limón en una mezcla fresca, vibrante y veraniega.</t>
   </si>
   <si>
     <t>Especiales</t>
@@ -363,6 +414,9 @@
     <t>Sleeper</t>
   </si>
   <si>
+    <t>Ron, vodka, melón y manzana en una mezcla suave, frutal y refrescante.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 ½ Oz De Ron Blanco Carta Blanca. 
 3 Oz De Vodka Absolut Blanco. 
 2 Oz De Sirope De Melon. 
@@ -378,6 +432,9 @@
     <t>Daiquiri</t>
   </si>
   <si>
+    <t>Ron blanco, limón y jarabe en una mezcla cítrica, equilibrada y directa.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 Oz Ron Carta Blanca  
 1 Oz Limon Zumo Fresco 
 1 ½ Almibar O Jarabe De Goma  
@@ -388,10 +445,13 @@
     <t>Copa Coupé</t>
   </si>
   <si>
-    <t>images/menu/alcohol/12-daiquiri.jpg</t>
+    <t>images/menu/alcohol/12-daiquiri.jpeg</t>
   </si>
   <si>
     <t>Hawaiian Blue </t>
+  </si>
+  <si>
+    <t>Ron, curaçao azul y piña en un cóctel tropical, llamativo y de perfil dulce.</t>
   </si>
   <si>
     <t xml:space="preserve">4 Onzas De Ron Blanco O Ron De Coco 
@@ -411,6 +471,9 @@
     <t>Tom Collis </t>
   </si>
   <si>
+    <t>Ginebra, limón y soda en un trago fresco, ligero y de perfil clásico.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 Oz Ginebra Aperitivo (Gordon”S) 
 1 Oz Jugo De Limón Fresco. 
 0.5 - 1 Oz Almíbar Simple (Jarabe De Azúcar). 
@@ -428,6 +491,9 @@
     <t>Cherry Champagne</t>
   </si>
   <si>
+    <t>Licor de cereza, ron y espumoso en una copa elegante, burbujeante y delicadamente frutal.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 Oz De Licor De Cereza O Almíbar De Cereza. 
 1 Oz Ron Blanco Carta Blanca  
 ½ Oz De Jarabe De Goma  
@@ -445,6 +511,9 @@
     <t>Tequila Sour Tropical</t>
   </si>
   <si>
+    <t>Tequila, limón, mango y naranja en una mezcla cítrica con un giro tropical y vibrante.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 ½ Oz Tequila Blanco. 
 ½ Oz Jugo De Limón O Lima Fresco. 
 1oz  Néctar O Jugo De Mango. 
@@ -460,6 +529,9 @@
   </si>
   <si>
     <t>Rouse Apple</t>
+  </si>
+  <si>
+    <t>Vodka, vino rosado y manzana en una mezcla frutal, suave y aromática.</t>
   </si>
   <si>
     <t xml:space="preserve">2 Oz De Vodka Adsolut  
@@ -475,6 +547,9 @@
   </si>
   <si>
     <t>Bulls Cantina </t>
+  </si>
+  <si>
+    <t>Ron, ginebra, tequila y limón en una mezcla intensa y fresca, rematada con cerveza.</t>
   </si>
   <si>
     <t>1.5 A 2 Onzas Carta Blanca. 
@@ -496,6 +571,9 @@
     <t>Rumba Zafari</t>
   </si>
   <si>
+    <t>Ron añejo, naranja, granadina y licor de fresa en un cóctel frutal, colorido y tropical.</t>
+  </si>
+  <si>
     <t>1 Oz  De Ron Añejo Bacardi. 
 100 Ml De Jugo De Naranja. 
 Hielo Al Frapee. 
@@ -510,6 +588,9 @@
   </si>
   <si>
     <t>Mains Zafiro</t>
+  </si>
+  <si>
+    <t>Aguardiente, ron y manzana verde en una mezcla de la casa con perfil fresco, frutal y distintivo.</t>
   </si>
   <si>
     <t>De la casa</t>
@@ -526,10 +607,13 @@
     <t>Copa Wishkero Ancho.</t>
   </si>
   <si>
-    <t>images/menu/house/20-mains-zafiro.jpg</t>
+    <t>images/menu/house/20-mains-zafiro.jpeg</t>
   </si>
   <si>
     <t>Micheldas (Frutos Rojos Verdes Amarillos)</t>
+  </si>
+  <si>
+    <t>Mezcla refrescante con soda, notas frutales y borde escarchado, pensada para una experiencia vibrante sin alcohol.</t>
   </si>
   <si>
     <t>Sin alcohol</t>
@@ -549,10 +633,13 @@
 Copa Chabela Alta</t>
   </si>
   <si>
-    <t>images/menu/non-alcohol/21-micheladas-surtidas.png</t>
-  </si>
-  <si>
-    <t>Long Islad</t>
+    <t>images/menu/non-alcohol/21-micheladas-surtidas.jpeg</t>
+  </si>
+  <si>
+    <t>Long Island</t>
+  </si>
+  <si>
+    <t>Mezcla sin alcohol con limón, soda y notas azules en un perfil fresco, dulce y llamativo.</t>
   </si>
   <si>
     <t xml:space="preserve">360 Ml De Gaseosa Sprite Limon Y Gaseosa 7up. 
@@ -569,6 +656,9 @@
   </si>
   <si>
     <t>Mojito Fresd </t>
+  </si>
+  <si>
+    <t>Limón, hierbabuena y soda en una versión sin alcohol, ligera y muy refrescante.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Oz De Zumo De Limón. 
@@ -588,6 +678,9 @@
     <t>Blue Lagoon Drop</t>
   </si>
   <si>
+    <t>Naranja, soda y cítricos en una mezcla azul, fresca y visualmente llamativa.</t>
+  </si>
+  <si>
     <t xml:space="preserve">120 Ml De Jugo De Naranja Fresco. 
 120 Ml De Soda O Agua Con Gas Saborizda. 
 Zumo Refresco De Limón. 
@@ -599,6 +692,9 @@
   </si>
   <si>
     <t>Soda Obush</t>
+  </si>
+  <si>
+    <t>Soda, limón y sal en una mezcla simple, refrescante y fácil de tomar.</t>
   </si>
   <si>
     <t xml:space="preserve">360 Ml De Soda 
@@ -736,7 +832,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -776,6 +872,29 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -812,7 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -850,6 +969,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1164,21 +1304,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="183.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="24.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="3"/>
+    <col min="9" max="9" width="17.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="12" customFormat="1">
+    <row r="1" spans="1:14" s="12" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1209,306 +1355,558 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="12">
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="12">
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="12">
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="12">
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="12">
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="12">
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="12">
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="12">
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="12">
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="12">
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="K16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="12">
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="K17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="12">
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="K18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" s="15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="12">
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="K19" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="12">
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="K20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="12">
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
+      <c r="K21" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="15">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1517,45 +1915,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E651A84-53CF-42A2-A53F-F3F82D40C10B}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.28515625" style="5" customWidth="1"/>
     <col min="8" max="8" width="50" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="66.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="5"/>
+    <col min="11" max="11" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" ht="18">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="18">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -1564,506 +1967,927 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="199.5">
+      <c r="K1" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="199.5">
       <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="215.25">
+        <v>62</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="22">
+        <v>1</v>
+      </c>
+      <c r="O2" s="22"/>
+    </row>
+    <row r="3" spans="1:15" ht="215.25">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>55</v>
+        <v>63</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>64</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="168">
+        <v>67</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="22">
+        <v>2</v>
+      </c>
+      <c r="O3" s="22"/>
+    </row>
+    <row r="4" spans="1:15" ht="168">
       <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="184.5">
+        <v>72</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="22">
+        <v>3</v>
+      </c>
+      <c r="O4" s="22"/>
+    </row>
+    <row r="5" spans="1:15" ht="184.5">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>73</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="184.5">
+        <v>77</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="22">
+        <v>4</v>
+      </c>
+      <c r="O5" s="22"/>
+    </row>
+    <row r="6" spans="1:15" ht="184.5">
       <c r="A6" s="10">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="153">
+        <v>82</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="22">
+        <v>5</v>
+      </c>
+      <c r="O6" s="22"/>
+    </row>
+    <row r="7" spans="1:15" ht="153">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>71</v>
+        <v>83</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="230.25">
+        <v>87</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="22">
+        <v>6</v>
+      </c>
+      <c r="O7" s="22"/>
+    </row>
+    <row r="8" spans="1:15" ht="230.25">
       <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>75</v>
+        <v>88</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>89</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="168">
+        <v>92</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="22">
+        <v>7</v>
+      </c>
+      <c r="O8" s="22"/>
+    </row>
+    <row r="9" spans="1:15" ht="168">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>93</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="107.25">
+        <v>97</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="22">
+        <v>8</v>
+      </c>
+      <c r="O9" s="22"/>
+    </row>
+    <row r="10" spans="1:15" ht="107.25">
       <c r="A10" s="10">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>83</v>
+        <v>98</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="199.5">
+        <v>102</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="22">
+        <v>9</v>
+      </c>
+      <c r="O10" s="22"/>
+    </row>
+    <row r="11" spans="1:15" ht="199.5">
       <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>87</v>
+        <v>103</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="215.25">
+        <v>108</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="22">
+        <v>10</v>
+      </c>
+      <c r="O11" s="22"/>
+    </row>
+    <row r="12" spans="1:15" ht="215.25">
       <c r="A12" s="10">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>92</v>
+        <v>109</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>110</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="153">
+        <v>112</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="22">
+        <v>11</v>
+      </c>
+      <c r="O12" s="22"/>
+    </row>
+    <row r="13" spans="1:15" ht="153">
       <c r="A13" s="10">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>95</v>
+        <v>113</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>97</v>
+        <v>116</v>
+      </c>
+      <c r="I13" s="5">
+        <v>20000</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="168">
+        <v>117</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="22">
+        <v>12</v>
+      </c>
+      <c r="O13" s="22"/>
+    </row>
+    <row r="14" spans="1:15" ht="168">
       <c r="A14" s="10">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>99</v>
+        <v>118</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="168">
+        <v>122</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="22">
+        <v>13</v>
+      </c>
+      <c r="O14" s="22"/>
+    </row>
+    <row r="15" spans="1:15" ht="168">
       <c r="A15" s="10">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>103</v>
+        <v>123</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>124</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="184.5">
+        <v>127</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="22">
+        <v>14</v>
+      </c>
+      <c r="O15" s="22"/>
+    </row>
+    <row r="16" spans="1:15" ht="184.5">
       <c r="A16" s="10">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>107</v>
+        <v>128</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>129</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="168">
+        <v>132</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="22">
+        <v>15</v>
+      </c>
+      <c r="O16" s="22"/>
+    </row>
+    <row r="17" spans="1:15" ht="168">
       <c r="A17" s="10">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>111</v>
+        <v>133</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="199.5">
+        <v>137</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" s="22">
+        <v>16</v>
+      </c>
+      <c r="O17" s="22"/>
+    </row>
+    <row r="18" spans="1:15" ht="199.5">
       <c r="A18" s="10">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>115</v>
+        <v>138</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>139</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="230.25">
+        <v>141</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" s="22">
+        <v>17</v>
+      </c>
+      <c r="O18" s="22"/>
+    </row>
+    <row r="19" spans="1:15" ht="230.25">
       <c r="A19" s="10">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>118</v>
+        <v>142</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>143</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="138">
+        <v>146</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="22">
+        <v>18</v>
+      </c>
+      <c r="O19" s="22"/>
+    </row>
+    <row r="20" spans="1:15" ht="138">
       <c r="A20" s="10">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>122</v>
+        <v>147</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="168">
+        <v>151</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="22">
+        <v>19</v>
+      </c>
+      <c r="O20" s="22"/>
+    </row>
+    <row r="21" spans="1:15" ht="168">
       <c r="A21" s="10">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>126</v>
+        <v>152</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="230.25">
+        <v>157</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="22">
+        <v>20</v>
+      </c>
+      <c r="O21" s="22"/>
+    </row>
+    <row r="22" spans="1:15" ht="230.25">
       <c r="A22" s="10">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>131</v>
+        <v>158</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>159</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>134</v>
+        <v>162</v>
+      </c>
+      <c r="I22" s="5">
+        <v>21000</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="138">
+        <v>163</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="22">
+        <v>21</v>
+      </c>
+      <c r="O22" s="22"/>
+    </row>
+    <row r="23" spans="1:15" ht="138">
       <c r="A23" s="10">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>136</v>
+        <v>164</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>165</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="168">
+        <v>168</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="22">
+        <v>22</v>
+      </c>
+      <c r="O23" s="22"/>
+    </row>
+    <row r="24" spans="1:15" ht="168">
       <c r="A24" s="10">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>140</v>
+        <v>169</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>170</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="153">
+        <v>173</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" s="22">
+        <v>23</v>
+      </c>
+      <c r="O24" s="22"/>
+    </row>
+    <row r="25" spans="1:15" ht="153">
       <c r="A25" s="10">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>144</v>
+        <v>174</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>175</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="91.5">
+        <v>177</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="22">
+        <v>24</v>
+      </c>
+      <c r="O25" s="22"/>
+    </row>
+    <row r="26" spans="1:15" ht="91.5">
       <c r="A26" s="10">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>147</v>
+        <v>178</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>179</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>150</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" s="22">
+        <v>25</v>
+      </c>
+      <c r="O26" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2072,43 +2896,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A989889E-D529-4390-8F71-069CF2800907}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:14" s="11" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -2117,439 +2947,823 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I2" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="11">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I3" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="11">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I4" s="14">
         <v>9000</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="11">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I5" s="14">
         <v>6000</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="11">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I6" s="14">
         <v>8000</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="11">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I7" s="14">
         <v>7000</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="11">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I8" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="11">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="I9" s="14">
         <v>13000</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="11">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="I10" s="14">
         <v>18000</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="11">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I11" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="11">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="I12" s="14">
         <v>3000</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="11">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="I13" s="14">
         <v>4000</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="11">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I14" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="11">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I15" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="11">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="I16" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="K16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="11">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I17" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="K17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="11">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I18" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="K18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" s="15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="11">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I19" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="K19" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="11">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="I20" s="14">
         <v>5000</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="K20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="11">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I21" s="14">
         <v>55000</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="K21" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="11">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I22" s="14">
         <v>55000</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="K22" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="11">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I23" s="14">
         <v>55000</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="K23" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="11">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I24" s="14">
         <v>95000</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="K24" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" s="15">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="11">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I25" s="14">
         <v>90000</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="K25" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="11">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I26" s="14">
         <v>55000</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="K26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" s="15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="11">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I27" s="14">
         <v>250000</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="K27" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" s="15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="11">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I28" s="14">
         <v>260000</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="K28" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" s="15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="11">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I29" s="14">
         <v>280000</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="K29" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" s="15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="11">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I30" s="14">
         <v>80000</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="K30" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" s="15">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="11">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I31" s="14">
         <v>120000</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="K31" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" s="15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="11">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I32" s="14">
         <v>380000</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" s="15">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{439BD3B3-8C9A-4053-BA1C-0A17AA823FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD9E7AE6-E4C8-4462-9344-FFA0B2524F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="250">
   <si>
     <t>No</t>
   </si>
@@ -711,121 +711,205 @@
     <t>images/menu/non-alcohol/25-soda-obush.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Poker </t>
+    <t>Poker</t>
   </si>
   <si>
     <t>Cervezas</t>
   </si>
   <si>
-    <t xml:space="preserve">Águila Original </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corona </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronita </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Club Colombia </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budweiser </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costeña </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smirnoff personal </t>
+    <t>images/menu/bebidas/poker.jpg</t>
+  </si>
+  <si>
+    <t>Águila Original</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/aguila-original.jpg</t>
+  </si>
+  <si>
+    <t>Corona</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/corona.jpg</t>
+  </si>
+  <si>
+    <t>Coronita</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/coronita.jpg</t>
+  </si>
+  <si>
+    <t>Club Colombia</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/club-colombia.jpg</t>
+  </si>
+  <si>
+    <t>Budweiser</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/budweiser.jpg</t>
+  </si>
+  <si>
+    <t>Costeña</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/costena.jpg</t>
+  </si>
+  <si>
+    <t>Smirnoff Ice Personal</t>
   </si>
   <si>
     <t>Cervezas preparadas</t>
   </si>
   <si>
-    <t xml:space="preserve">Stella </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coca-Cola </t>
+    <t>images/menu/bebidas/smirnoff-ice-personal.jpg</t>
+  </si>
+  <si>
+    <t>Stella Artois</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/stella-artois.jpg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
   </si>
   <si>
     <t>Gaseosas</t>
   </si>
   <si>
-    <t xml:space="preserve">Agua Cristal </t>
+    <t>images/menu/bebidas/coca-cola.jpg</t>
+  </si>
+  <si>
+    <t>Agua Cristal</t>
   </si>
   <si>
     <t>Aguas</t>
   </si>
   <si>
-    <t xml:space="preserve">Agua con gas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada Dry </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprite </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jugo Hit surtido </t>
+    <t>images/menu/bebidas/agua-cristal.jpg</t>
+  </si>
+  <si>
+    <t>Agua con Gas</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/agua-con-gas.jpg</t>
+  </si>
+  <si>
+    <t>Canada Dry</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/canada-dry.jpg</t>
+  </si>
+  <si>
+    <t>Sprite</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/sprite.jpg</t>
+  </si>
+  <si>
+    <t>Jugo Hit Surtido</t>
   </si>
   <si>
     <t>Jugos</t>
   </si>
   <si>
-    <t xml:space="preserve">Gaseosa surtida Postobón </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed Max </t>
+    <t>images/menu/bebidas/jugo-hit-surtido.jpg</t>
+  </si>
+  <si>
+    <t>Gaseosa Surtida Postobón</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/gaseosa-surtida-postobon.jpg</t>
+  </si>
+  <si>
+    <t>Speed Max</t>
   </si>
   <si>
     <t>Energizantes</t>
   </si>
   <si>
-    <t xml:space="preserve">Squash personal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bretaña / Soda </t>
+    <t>images/menu/bebidas/speed-max.jpg</t>
+  </si>
+  <si>
+    <t>Squash Personal</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/squash-personal.jpg</t>
+  </si>
+  <si>
+    <t>Bretaña / Soda</t>
   </si>
   <si>
     <t>Mezcladores</t>
   </si>
   <si>
-    <t xml:space="preserve">Aguardiente negro / verde media </t>
+    <t>images/menu/bebidas/bretana-soda.jpg</t>
+  </si>
+  <si>
+    <t>Aguardiente Negro / Verde Media</t>
   </si>
   <si>
     <t>Licores</t>
   </si>
   <si>
-    <t xml:space="preserve">Aguardiente azul media </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amarillo pequeño </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amarillo grande </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ron viejo de caldas grande </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ron viejo de caldas pequeño </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old Parr grande </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buchanan’s Deluxe </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buchanan’s Master </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grands pequeña </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grands grande </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don Julio Blanco </t>
+    <t>images/menu/bebidas/aguardiente-negro-verde.jpg</t>
+  </si>
+  <si>
+    <t>Aguardiente Azul Media</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/aguardiente-azul.jpg</t>
+  </si>
+  <si>
+    <t>Aguardiente Amarillo Media</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/aguardiente-amarillo.jpg</t>
+  </si>
+  <si>
+    <t>Aguardiente Amarillo Botella</t>
+  </si>
+  <si>
+    <t>Ron Viejo de Caldas Botella</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/ron-viejo-de-caldas.jpg</t>
+  </si>
+  <si>
+    <t>Ron Viejo de Caldas Media</t>
+  </si>
+  <si>
+    <t>Old Parr Botella</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/old-parr.jpg</t>
+  </si>
+  <si>
+    <t>Buchanan’s Deluxe Botella</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/buchanans-deluxe.jpg</t>
+  </si>
+  <si>
+    <t>Buchanan’s Master Botella</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/buchanans-master.jpg</t>
+  </si>
+  <si>
+    <t>Grant’s Media</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/grants.jpg</t>
+  </si>
+  <si>
+    <t>Grant’s Botella</t>
+  </si>
+  <si>
+    <t>Don Julio Blanco Botella</t>
+  </si>
+  <si>
+    <t>images/menu/bebidas/don-julio-blanco.jpg</t>
   </si>
 </sst>
 </file>
@@ -2908,7 +2992,7 @@
     <col min="7" max="7" width="17.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="43.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
@@ -2973,6 +3057,9 @@
       <c r="I2" s="14">
         <v>5000</v>
       </c>
+      <c r="J2" t="s">
+        <v>185</v>
+      </c>
       <c r="K2" s="15" t="s">
         <v>16</v>
       </c>
@@ -2991,13 +3078,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>184</v>
       </c>
       <c r="I3" s="14">
         <v>5000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>187</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>16</v>
@@ -3017,13 +3107,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>184</v>
       </c>
       <c r="I4" s="14">
         <v>9000</v>
+      </c>
+      <c r="J4" t="s">
+        <v>189</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>16</v>
@@ -3043,13 +3136,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>184</v>
       </c>
       <c r="I5" s="14">
         <v>6000</v>
+      </c>
+      <c r="J5" t="s">
+        <v>191</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>16</v>
@@ -3069,13 +3165,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>184</v>
       </c>
       <c r="I6" s="14">
         <v>8000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>193</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>16</v>
@@ -3095,13 +3194,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>184</v>
       </c>
       <c r="I7" s="14">
         <v>7000</v>
+      </c>
+      <c r="J7" t="s">
+        <v>195</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>16</v>
@@ -3121,13 +3223,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>184</v>
       </c>
       <c r="I8" s="14">
         <v>5000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>197</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>16</v>
@@ -3147,13 +3252,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="I9" s="14">
         <v>13000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>200</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>16</v>
@@ -3173,13 +3281,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>184</v>
       </c>
       <c r="I10" s="14">
         <v>18000</v>
+      </c>
+      <c r="J10" t="s">
+        <v>202</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>16</v>
@@ -3199,13 +3310,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I11" s="14">
         <v>5000</v>
+      </c>
+      <c r="J11" t="s">
+        <v>205</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>16</v>
@@ -3225,13 +3339,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I12" s="14">
         <v>3000</v>
+      </c>
+      <c r="J12" t="s">
+        <v>208</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>16</v>
@@ -3251,13 +3368,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I13" s="14">
         <v>4000</v>
+      </c>
+      <c r="J13" t="s">
+        <v>210</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>16</v>
@@ -3277,13 +3397,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I14" s="14">
         <v>5000</v>
+      </c>
+      <c r="J14" t="s">
+        <v>212</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>16</v>
@@ -3303,13 +3426,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I15" s="14">
         <v>5000</v>
+      </c>
+      <c r="J15" t="s">
+        <v>214</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>16</v>
@@ -3329,14 +3455,17 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="I16" s="14">
         <v>5000</v>
       </c>
+      <c r="J16" t="s">
+        <v>217</v>
+      </c>
       <c r="K16" s="15" t="s">
         <v>16</v>
       </c>
@@ -3355,14 +3484,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I17" s="14">
         <v>5000</v>
       </c>
+      <c r="J17" t="s">
+        <v>219</v>
+      </c>
       <c r="K17" s="15" t="s">
         <v>16</v>
       </c>
@@ -3381,13 +3513,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="I18" s="14">
         <v>5000</v>
+      </c>
+      <c r="J18" t="s">
+        <v>222</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>16</v>
@@ -3407,13 +3542,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I19" s="14">
         <v>5000</v>
+      </c>
+      <c r="J19" t="s">
+        <v>224</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>16</v>
@@ -3433,13 +3571,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="I20" s="14">
         <v>5000</v>
+      </c>
+      <c r="J20" t="s">
+        <v>227</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>16</v>
@@ -3459,13 +3600,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I21" s="14">
         <v>55000</v>
+      </c>
+      <c r="J21" t="s">
+        <v>230</v>
       </c>
       <c r="K21" s="15" t="s">
         <v>16</v>
@@ -3485,13 +3629,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I22" s="14">
         <v>55000</v>
+      </c>
+      <c r="J22" t="s">
+        <v>232</v>
       </c>
       <c r="K22" s="15" t="s">
         <v>16</v>
@@ -3511,13 +3658,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I23" s="14">
         <v>55000</v>
+      </c>
+      <c r="J23" t="s">
+        <v>234</v>
       </c>
       <c r="K23" s="15" t="s">
         <v>16</v>
@@ -3537,13 +3687,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I24" s="14">
         <v>95000</v>
+      </c>
+      <c r="J24" t="s">
+        <v>234</v>
       </c>
       <c r="K24" s="15" t="s">
         <v>16</v>
@@ -3563,13 +3716,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I25" s="14">
         <v>90000</v>
+      </c>
+      <c r="J25" t="s">
+        <v>237</v>
       </c>
       <c r="K25" s="15" t="s">
         <v>16</v>
@@ -3589,13 +3745,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I26" s="14">
         <v>55000</v>
+      </c>
+      <c r="J26" t="s">
+        <v>237</v>
       </c>
       <c r="K26" s="15" t="s">
         <v>16</v>
@@ -3615,13 +3774,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I27" s="14">
         <v>250000</v>
+      </c>
+      <c r="J27" t="s">
+        <v>240</v>
       </c>
       <c r="K27" s="15" t="s">
         <v>16</v>
@@ -3641,13 +3803,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I28" s="14">
         <v>260000</v>
+      </c>
+      <c r="J28" t="s">
+        <v>242</v>
       </c>
       <c r="K28" s="15" t="s">
         <v>16</v>
@@ -3667,13 +3832,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I29" s="14">
         <v>280000</v>
+      </c>
+      <c r="J29" t="s">
+        <v>244</v>
       </c>
       <c r="K29" s="15" t="s">
         <v>16</v>
@@ -3693,13 +3861,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I30" s="14">
         <v>80000</v>
+      </c>
+      <c r="J30" t="s">
+        <v>246</v>
       </c>
       <c r="K30" s="15" t="s">
         <v>16</v>
@@ -3719,13 +3890,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I31" s="14">
         <v>120000</v>
+      </c>
+      <c r="J31" t="s">
+        <v>246</v>
       </c>
       <c r="K31" s="15" t="s">
         <v>16</v>
@@ -3745,13 +3919,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I32" s="14">
         <v>380000</v>
+      </c>
+      <c r="J32" t="s">
+        <v>249</v>
       </c>
       <c r="K32" s="15" t="s">
         <v>16</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD9E7AE6-E4C8-4462-9344-FFA0B2524F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE02C74E-92A1-4AA1-B2A3-45CFBDE8297B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="256">
   <si>
     <t>No</t>
   </si>
@@ -77,13 +77,16 @@
     <t>Orden</t>
   </si>
   <si>
-    <t>Tortilla Carne de Zafiro</t>
-  </si>
-  <si>
-    <t>Tortilla rellena de queso fundiddo ° Carne desmechada y aguacate con ahogao</t>
-  </si>
-  <si>
-    <t>SI</t>
+    <t>Tortilla Carne Zafiro</t>
+  </si>
+  <si>
+    <t>Tortilla rellena de queso fundiddo, carne o pollo desmechada y aguacate con ahogao.</t>
+  </si>
+  <si>
+    <t>Entradas</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
   <si>
     <t>NO</t>
@@ -92,97 +95,109 @@
     <t>Corn Dog Zafiro Bites</t>
   </si>
   <si>
-    <t>Mini corn dogs crujientes · miel mostaza ketchup artesanal.</t>
-  </si>
-  <si>
-    <t>Tostones cartageneros</t>
-  </si>
-  <si>
-    <t>Patacones con ahoago, acompañado de carne desmechada y aguacate</t>
+    <t>Mini corn dogs crujientes, miel mostaza y ketchup artesanal.</t>
+  </si>
+  <si>
+    <t>Tostones Cartageneros</t>
+  </si>
+  <si>
+    <t>Patacones con ahogao, acompañado de carne desmechada y aguacate.</t>
   </si>
   <si>
     <t>Nachos Zafiro</t>
   </si>
   <si>
-    <t>Totopos, carne desmechada, cheddar fundido · pico de gallo · guacamole · crema agria</t>
+    <t>Totopos, carne desmechada, cheddar fundido, pico de gallo, guacamole y crema agria.</t>
+  </si>
+  <si>
+    <t>Para compartir</t>
   </si>
   <si>
     <t>Huevos Ahogados</t>
   </si>
   <si>
-    <t>Cacerola de huevos añ horno con ahogado y brotes.</t>
+    <t>Cacerola de huevos al horno con ahogao y brotes.</t>
   </si>
   <si>
     <t>Choripan Argentino</t>
   </si>
   <si>
-    <t>Pan baggete crijiente, Chorizo en forma de mariposa, acompañado de salsa de cilantro con perejil, y papas rusticas con paprikka.</t>
+    <t>Pan baggete crujiente, chorizo en forma de mariposa, acompañado de salsa de cilantro con perejil y papas rusticas con paprikka.</t>
+  </si>
+  <si>
+    <t>Sanduches y perros</t>
   </si>
   <si>
     <t>Perrito Loco</t>
   </si>
   <si>
-    <t>Salchicha americana, acompañado de guacamole, queso crema, queso cheddar, y tcineta en laminas</t>
-  </si>
-  <si>
-    <t>REINA PEPIADA</t>
-  </si>
-  <si>
-    <t>Sándwich relleno de queso crema, cebolla en brunoise, aguacate y pollo</t>
+    <t>Salchicha americana, acompañado de guacamole, queso crema, queso cheddar, y tocineta en laminas.</t>
+  </si>
+  <si>
+    <t>Reina Pepiada</t>
+  </si>
+  <si>
+    <t>Sándwich relleno con doble queso crema, cebolla en brunoise, aguacate y pollo.</t>
   </si>
   <si>
     <t>Pinchos de Papas Fundidas</t>
   </si>
   <si>
-    <t>Papas a la francesa montadas en brocheta, queso gratinado, cebolla morada y pimentón, toque de salsa.</t>
+    <t>Papas a la francesa montadas en brocheta, queso gratinado, cebolla morada, pimentón y un toque de salsa.</t>
   </si>
   <si>
     <t>Bocados Costa Zafiro</t>
   </si>
   <si>
-    <t>Totopos/tartaletas, base de guacamole, camarón salteado al limón, cilantro.</t>
+    <t>Totopos/tartaletas, base de guacamole, camarón salteado al limón y cilantro.</t>
   </si>
   <si>
     <t>Tortillas al Zafiro</t>
   </si>
   <si>
-    <t>Dos tortillas rellenas con carne en laminas, doble queso crema de leche, mantequilla y cilantro fresco</t>
-  </si>
-  <si>
-    <t>Desgranado El recucitador</t>
-  </si>
-  <si>
-    <t>Base de lechuga, papas rusticas, con pollo y carne desmechada, chorizo, tocineta, maiz tierno,</t>
+    <t>Dos tortillas rellenas con carne en laminas, doble queso crema de leche, mantequilla y cilantro fresco.</t>
+  </si>
+  <si>
+    <t>Desgranado El Recucitador</t>
+  </si>
+  <si>
+    <t>Base de lechuga, papas rusticas, con pollo y carne desmechada, chorizo, tocineta y maiz tierno.</t>
   </si>
   <si>
     <t>Hamburguesa de la Casa</t>
   </si>
   <si>
-    <t>Pan Artesanal, carnde de 150gr, cebolla encurtida, tocineta dulce, queso cheddar. lechuaga, tomate y salsa de la casa</t>
+    <t>Pan artesanal, carne de 150gr, cebolla encurtida, tocineta dulce, queso cheddar, lechuaga, tomate y salsa de la casa.</t>
+  </si>
+  <si>
+    <t>Hamburguesas</t>
   </si>
   <si>
     <t>La Reina Doble</t>
   </si>
   <si>
-    <t>Pan Artesanal, carne de 110gr, boble queso, doble tocineta, huevo frito, salsa de Ajo y bbq, lechuga y tomate frescos.</t>
+    <t>Pan artesanal, doble carne de 110gr, boble queso, doble tocineta, huevo frito, salsa de Ajo y BBQ, lechuga y tomate frescos.</t>
   </si>
   <si>
     <t>La Diabla</t>
   </si>
   <si>
-    <t>Pan artesanal, carne de 110gr, carne desmechada, queso crema, aguacate, tocineta, jalapeños, cebolla salteada, salsa habanera, lechuga y tomate</t>
-  </si>
-  <si>
-    <t>La original</t>
-  </si>
-  <si>
-    <t>Pan artesanal, carnde 110gr, tocineta, queso doble crema, chorizo, lechuga y tomate</t>
-  </si>
-  <si>
-    <t>Helado con brownie</t>
-  </si>
-  <si>
-    <t>Tres bolas de helado, con un brownie en trozos pequeños, acompañados de salsa de chocolate</t>
+    <t>Pan artesanal, carne de 110gr, carne desmechada, queso crema, aguacate, tocineta, jalapeños, cebolla salteada, salsa habanera, lechuga y tomate.</t>
+  </si>
+  <si>
+    <t>La Original</t>
+  </si>
+  <si>
+    <t>Pan artesanal, carnde 110gr, tocineta, queso doble crema, chorizo, lechuga y tomate.</t>
+  </si>
+  <si>
+    <t>Helado con Brownie</t>
+  </si>
+  <si>
+    <t>Tres bolas de helado, con un brownie en trozos pequeños, acompañados de salsa de chocolate.</t>
+  </si>
+  <si>
+    <t>Postres</t>
   </si>
   <si>
     <t>Creep Achocolatado</t>
@@ -191,16 +206,16 @@
     <t>Base de helado, con frutos rojos o amarillos, con nutella y salsa de chocolate.</t>
   </si>
   <si>
-    <t>brownie con Helado</t>
-  </si>
-  <si>
-    <t>Brownie con una bola de helado, acompañado de salasa de chocolate, fresas y arandanos,</t>
+    <t>Brownie con Helado</t>
+  </si>
+  <si>
+    <t>Brownie con una bola de helado, acompañado de salsa de chocolate, fresas y arandanos.</t>
   </si>
   <si>
     <t>Tostadas con Amor</t>
   </si>
   <si>
-    <t>Pan tajado crujiente, con base de nnutella, fresas, arandanos, melocoton y menta fresca.</t>
+    <t>Pan tajado crujiente, con base de nutella, fresas, arandanos, melocoton y menta fresca.</t>
   </si>
   <si>
     <t> </t>
@@ -227,6 +242,9 @@
   </si>
   <si>
     <t>images/menu/alcohol/01-margaritas-surtidas.jpeg</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
   <si>
     <t>Coctel Tequila Sunrise </t>
@@ -1395,7 +1413,7 @@
     <col min="2" max="2" width="35.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="183.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -1463,17 +1481,22 @@
         <v>15</v>
       </c>
       <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="K2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>16</v>
+      <c r="I2">
+        <v>21000</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" s="15">
         <v>1</v>
@@ -1484,23 +1507,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="K3" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>16</v>
+      <c r="I3">
+        <v>18000</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" s="15">
         <v>2</v>
@@ -1511,23 +1539,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="K4" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>16</v>
+      <c r="I4">
+        <v>20000</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4" s="15">
         <v>3</v>
@@ -1538,23 +1571,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
-      <c r="K5" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>16</v>
+      <c r="I5">
+        <v>24000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N5" s="15">
         <v>4</v>
@@ -1565,23 +1603,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
-      <c r="K6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>16</v>
+      <c r="I6">
+        <v>15000</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" t="s">
+        <v>17</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" s="15">
         <v>5</v>
@@ -1592,23 +1635,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
-      <c r="K7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>16</v>
+      <c r="I7">
+        <v>20000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" s="15">
         <v>6</v>
@@ -1619,23 +1667,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
-      <c r="K8" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>16</v>
+      <c r="I8">
+        <v>19000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N8" s="15">
         <v>7</v>
@@ -1646,23 +1699,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-      <c r="K9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>16</v>
+      <c r="I9">
+        <v>21000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9" s="15">
         <v>8</v>
@@ -1673,23 +1731,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
-      <c r="K10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>16</v>
+      <c r="I10">
+        <v>18000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>0</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" s="15">
         <v>9</v>
@@ -1700,23 +1763,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
-      <c r="K11" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>16</v>
+      <c r="I11">
+        <v>26000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11" s="15">
         <v>10</v>
@@ -1727,23 +1795,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
-      <c r="K12" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>16</v>
+      <c r="I12">
+        <v>23000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N12" s="15">
         <v>11</v>
@@ -1754,23 +1827,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
-      <c r="K13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>16</v>
+      <c r="I13">
+        <v>29000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" s="15">
         <v>12</v>
@@ -1781,23 +1859,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
-      <c r="K14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>16</v>
+      <c r="I14">
+        <v>24000</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N14" s="15">
         <v>13</v>
@@ -1808,23 +1891,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
-      <c r="K15" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>16</v>
+      <c r="I15">
+        <v>28000</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" s="15">
         <v>14</v>
@@ -1835,23 +1923,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
-      <c r="K16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>16</v>
+      <c r="I16">
+        <v>28000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N16" s="15">
         <v>15</v>
@@ -1862,23 +1955,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
-      <c r="K17" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>16</v>
+      <c r="I17">
+        <v>24000</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N17" s="15">
         <v>16</v>
@@ -1889,23 +1987,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
-      <c r="K18" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>16</v>
+      <c r="I18">
+        <v>17000</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N18" s="15">
         <v>17</v>
@@ -1916,23 +2019,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="K19" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>16</v>
+      <c r="I19">
+        <v>19000</v>
+      </c>
+      <c r="K19" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>0</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N19" s="15">
         <v>18</v>
@@ -1943,23 +2051,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
-      <c r="K20" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>16</v>
+      <c r="I20">
+        <v>17000</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N20" s="15">
         <v>19</v>
@@ -1970,23 +2083,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
-      <c r="K21" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>16</v>
+      <c r="I21">
+        <v>17000</v>
+      </c>
+      <c r="K21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" t="s">
+        <v>17</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N21" s="15">
         <v>20</v>
@@ -2064,7 +2182,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="199.5">
@@ -2072,31 +2190,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M2" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" s="22">
         <v>1</v>
@@ -2108,31 +2226,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" s="22">
         <v>2</v>
@@ -2144,31 +2262,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4" s="22">
         <v>3</v>
@@ -2180,31 +2298,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N5" s="22">
         <v>4</v>
@@ -2216,31 +2334,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" s="22">
         <v>5</v>
@@ -2252,31 +2370,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" s="22">
         <v>6</v>
@@ -2288,31 +2406,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N8" s="22">
         <v>7</v>
@@ -2324,31 +2442,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9" s="22">
         <v>8</v>
@@ -2360,31 +2478,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" s="22">
         <v>9</v>
@@ -2396,31 +2514,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11" s="22">
         <v>10</v>
@@ -2432,31 +2550,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N12" s="22">
         <v>11</v>
@@ -2468,34 +2586,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I13" s="5">
         <v>20000</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" s="22">
         <v>12</v>
@@ -2507,31 +2625,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N14" s="22">
         <v>13</v>
@@ -2543,31 +2661,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" s="22">
         <v>14</v>
@@ -2579,31 +2697,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N16" s="22">
         <v>15</v>
@@ -2615,31 +2733,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M17" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N17" s="22">
         <v>16</v>
@@ -2651,31 +2769,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N18" s="22">
         <v>17</v>
@@ -2687,31 +2805,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N19" s="22">
         <v>18</v>
@@ -2723,31 +2841,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M20" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N20" s="22">
         <v>19</v>
@@ -2759,31 +2877,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N21" s="22">
         <v>20</v>
@@ -2795,34 +2913,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="I22" s="5">
         <v>21000</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M22" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N22" s="22">
         <v>21</v>
@@ -2834,31 +2952,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M23" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N23" s="22">
         <v>22</v>
@@ -2870,31 +2988,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M24" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N24" s="22">
         <v>23</v>
@@ -2906,31 +3024,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M25" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N25" s="22">
         <v>24</v>
@@ -2942,31 +3060,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M26" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N26" s="22">
         <v>25</v>
@@ -3049,25 +3167,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I2" s="14">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" s="15">
         <v>1</v>
@@ -3078,25 +3196,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I3" s="14">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" s="15">
         <v>2</v>
@@ -3107,25 +3225,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I4" s="14">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4" s="15">
         <v>3</v>
@@ -3136,25 +3254,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="I5" s="14">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N5" s="15">
         <v>4</v>
@@ -3165,25 +3283,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I6" s="14">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" s="15">
         <v>5</v>
@@ -3194,25 +3312,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I7" s="14">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" s="15">
         <v>6</v>
@@ -3223,25 +3341,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I8" s="14">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N8" s="15">
         <v>7</v>
@@ -3252,25 +3370,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I9" s="14">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9" s="15">
         <v>8</v>
@@ -3281,25 +3399,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I10" s="14">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" s="15">
         <v>9</v>
@@ -3310,25 +3428,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I11" s="14">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11" s="15">
         <v>10</v>
@@ -3339,25 +3457,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I12" s="14">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N12" s="15">
         <v>11</v>
@@ -3368,25 +3486,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I13" s="14">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" s="15">
         <v>12</v>
@@ -3397,25 +3515,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I14" s="14">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N14" s="15">
         <v>13</v>
@@ -3426,25 +3544,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I15" s="14">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" s="15">
         <v>14</v>
@@ -3455,25 +3573,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I16" s="14">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N16" s="15">
         <v>15</v>
@@ -3484,25 +3602,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I17" s="14">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N17" s="15">
         <v>16</v>
@@ -3513,25 +3631,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I18" s="14">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N18" s="15">
         <v>17</v>
@@ -3542,25 +3660,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I19" s="14">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N19" s="15">
         <v>18</v>
@@ -3571,25 +3689,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I20" s="14">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N20" s="15">
         <v>19</v>
@@ -3600,25 +3718,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I21" s="14">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N21" s="15">
         <v>20</v>
@@ -3629,25 +3747,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I22" s="14">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M22" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N22" s="15">
         <v>21</v>
@@ -3658,25 +3776,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I23" s="14">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N23" s="15">
         <v>22</v>
@@ -3687,25 +3805,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="I24" s="14">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N24" s="15">
         <v>23</v>
@@ -3716,25 +3834,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I25" s="14">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N25" s="15">
         <v>24</v>
@@ -3745,25 +3863,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I26" s="14">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N26" s="15">
         <v>25</v>
@@ -3774,25 +3892,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I27" s="14">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N27" s="15">
         <v>26</v>
@@ -3803,25 +3921,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I28" s="14">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M28" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N28" s="15">
         <v>27</v>
@@ -3832,25 +3950,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I29" s="14">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M29" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N29" s="15">
         <v>28</v>
@@ -3861,25 +3979,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I30" s="14">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M30" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N30" s="15">
         <v>29</v>
@@ -3890,25 +4008,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I31" s="14">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M31" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N31" s="15">
         <v>30</v>
@@ -3919,25 +4037,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I32" s="14">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N32" s="15">
         <v>31</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE02C74E-92A1-4AA1-B2A3-45CFBDE8297B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D2822A8-766E-4111-828E-B44A5316BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
     <sheet name="Cocteles" sheetId="3" r:id="rId2"/>
-    <sheet name="Bebidas" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
+    <sheet name="Bebidas" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="285">
   <si>
     <t>No</t>
   </si>
@@ -729,6 +730,93 @@
     <t>images/menu/non-alcohol/25-soda-obush.jpg</t>
   </si>
   <si>
+    <t>Producto</t>
+  </si>
+  <si>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>Margarita</t>
+  </si>
+  <si>
+    <t>Tequila Sunrise</t>
+  </si>
+  <si>
+    <t>Orgasmo</t>
+  </si>
+  <si>
+    <t>Cuba Libre</t>
+  </si>
+  <si>
+    <t>El Padrino</t>
+  </si>
+  <si>
+    <t>Piña Colada</t>
+  </si>
+  <si>
+    <t>Gin Tonic</t>
+  </si>
+  <si>
+    <t>Dry Martini</t>
+  </si>
+  <si>
+    <t>Passion Fresh</t>
+  </si>
+  <si>
+    <t>Hawaiian Blue</t>
+  </si>
+  <si>
+    <t>Ton Collis</t>
+  </si>
+  <si>
+    <t>Rouse Apple</t>
+  </si>
+  <si>
+    <t>Bulls Cantina</t>
+  </si>
+  <si>
+    <t>Rumba Zafari</t>
+  </si>
+  <si>
+    <t>Mains Zafiro</t>
+  </si>
+  <si>
+    <t>Long Islad</t>
+  </si>
+  <si>
+    <t>Mojito Fresd</t>
+  </si>
+  <si>
+    <t>Blue Lagoon Drop</t>
+  </si>
+  <si>
+    <t>Soda Obush</t>
+  </si>
+  <si>
+    <t>Michelada Premium Frutal</t>
+  </si>
+  <si>
+    <t>Michelada Frutal</t>
+  </si>
+  <si>
+    <t>Michelada Premium Clásica</t>
+  </si>
+  <si>
+    <t>Michelada Clásica</t>
+  </si>
+  <si>
+    <t>Michelada Sin Alcohol Frutal</t>
+  </si>
+  <si>
+    <t>Michelada Sin Alcohol Clásica</t>
+  </si>
+  <si>
+    <t>Michelada Ginger Ale Frutal</t>
+  </si>
+  <si>
+    <t>Michelada Ginger Ale</t>
+  </si>
+  <si>
     <t>Poker</t>
   </si>
   <si>
@@ -934,7 +1022,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -997,6 +1085,14 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1033,7 +1129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1092,6 +1188,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2204,6 +2303,9 @@
       <c r="H2" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="I2" s="25">
+        <v>22000</v>
+      </c>
       <c r="J2" s="5" t="s">
         <v>67</v>
       </c>
@@ -2240,6 +2342,9 @@
       <c r="H3" s="7" t="s">
         <v>72</v>
       </c>
+      <c r="I3" s="25">
+        <v>20000</v>
+      </c>
       <c r="J3" s="5" t="s">
         <v>73</v>
       </c>
@@ -2276,6 +2381,9 @@
       <c r="H4" s="8" t="s">
         <v>77</v>
       </c>
+      <c r="I4" s="25">
+        <v>22000</v>
+      </c>
       <c r="J4" s="5" t="s">
         <v>78</v>
       </c>
@@ -2312,6 +2420,9 @@
       <c r="H5" s="7" t="s">
         <v>82</v>
       </c>
+      <c r="I5" s="25">
+        <v>18000</v>
+      </c>
       <c r="J5" s="5" t="s">
         <v>83</v>
       </c>
@@ -2348,6 +2459,9 @@
       <c r="H6" s="7" t="s">
         <v>87</v>
       </c>
+      <c r="I6" s="25">
+        <v>20000</v>
+      </c>
       <c r="J6" s="5" t="s">
         <v>88</v>
       </c>
@@ -2384,6 +2498,9 @@
       <c r="H7" s="5" t="s">
         <v>92</v>
       </c>
+      <c r="I7" s="25">
+        <v>22000</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>93</v>
       </c>
@@ -2420,6 +2537,9 @@
       <c r="H8" s="5" t="s">
         <v>97</v>
       </c>
+      <c r="I8" s="25">
+        <v>22000</v>
+      </c>
       <c r="J8" s="5" t="s">
         <v>98</v>
       </c>
@@ -2456,6 +2576,9 @@
       <c r="H9" s="5" t="s">
         <v>102</v>
       </c>
+      <c r="I9" s="25">
+        <v>22000</v>
+      </c>
       <c r="J9" s="5" t="s">
         <v>103</v>
       </c>
@@ -2492,6 +2615,9 @@
       <c r="H10" s="7" t="s">
         <v>107</v>
       </c>
+      <c r="I10" s="25">
+        <v>20000</v>
+      </c>
       <c r="J10" s="5" t="s">
         <v>108</v>
       </c>
@@ -2528,6 +2654,9 @@
       <c r="H11" s="7" t="s">
         <v>113</v>
       </c>
+      <c r="I11" s="25">
+        <v>20000</v>
+      </c>
       <c r="J11" s="5" t="s">
         <v>114</v>
       </c>
@@ -2564,6 +2693,9 @@
       <c r="H12" s="8" t="s">
         <v>107</v>
       </c>
+      <c r="I12" s="25">
+        <v>20000</v>
+      </c>
       <c r="J12" s="5" t="s">
         <v>118</v>
       </c>
@@ -2600,7 +2732,7 @@
       <c r="H13" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="26">
         <v>20000</v>
       </c>
       <c r="J13" s="5" t="s">
@@ -2639,6 +2771,9 @@
       <c r="H14" s="8" t="s">
         <v>127</v>
       </c>
+      <c r="I14" s="25">
+        <v>22000</v>
+      </c>
       <c r="J14" s="5" t="s">
         <v>128</v>
       </c>
@@ -2675,6 +2810,9 @@
       <c r="H15" s="8" t="s">
         <v>132</v>
       </c>
+      <c r="I15" s="25">
+        <v>20000</v>
+      </c>
       <c r="J15" s="5" t="s">
         <v>133</v>
       </c>
@@ -2711,6 +2849,9 @@
       <c r="H16" s="8" t="s">
         <v>137</v>
       </c>
+      <c r="I16" s="25">
+        <v>22000</v>
+      </c>
       <c r="J16" s="5" t="s">
         <v>138</v>
       </c>
@@ -2747,6 +2888,9 @@
       <c r="H17" s="7" t="s">
         <v>142</v>
       </c>
+      <c r="I17" s="25">
+        <v>22000</v>
+      </c>
       <c r="J17" s="5" t="s">
         <v>143</v>
       </c>
@@ -2783,6 +2927,9 @@
       <c r="H18" s="7" t="s">
         <v>107</v>
       </c>
+      <c r="I18" s="25">
+        <v>20000</v>
+      </c>
       <c r="J18" s="5" t="s">
         <v>147</v>
       </c>
@@ -2818,6 +2965,9 @@
       </c>
       <c r="H19" s="8" t="s">
         <v>151</v>
+      </c>
+      <c r="I19" s="25">
+        <v>22000</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>152</v>
@@ -2855,6 +3005,9 @@
       <c r="H20" s="8" t="s">
         <v>156</v>
       </c>
+      <c r="I20" s="25">
+        <v>22000</v>
+      </c>
       <c r="J20" s="5" t="s">
         <v>157</v>
       </c>
@@ -2891,6 +3044,9 @@
       <c r="H21" s="8" t="s">
         <v>162</v>
       </c>
+      <c r="I21" s="25">
+        <v>25000</v>
+      </c>
       <c r="J21" s="5" t="s">
         <v>163</v>
       </c>
@@ -2927,7 +3083,7 @@
       <c r="H22" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="26">
         <v>21000</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -2966,6 +3122,9 @@
       <c r="H23" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="I23" s="25">
+        <v>15000</v>
+      </c>
       <c r="J23" s="5" t="s">
         <v>174</v>
       </c>
@@ -3002,6 +3161,9 @@
       <c r="H24" s="8" t="s">
         <v>178</v>
       </c>
+      <c r="I24" s="25">
+        <v>15000</v>
+      </c>
       <c r="J24" s="5" t="s">
         <v>179</v>
       </c>
@@ -3038,6 +3200,9 @@
       <c r="H25" s="8" t="s">
         <v>132</v>
       </c>
+      <c r="I25" s="25">
+        <v>15000</v>
+      </c>
       <c r="J25" s="5" t="s">
         <v>183</v>
       </c>
@@ -3073,6 +3238,9 @@
       </c>
       <c r="H26" s="8" t="s">
         <v>187</v>
+      </c>
+      <c r="I26" s="25">
+        <v>13000</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>188</v>
@@ -3097,6 +3265,283 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BCC74E-788A-40B0-B92B-C30392239841}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B15">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B24">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B26">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B29">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>214</v>
+      </c>
+      <c r="B30">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>217</v>
+      </c>
+      <c r="B33">
+        <v>14000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A989889E-D529-4390-8F71-069CF2800907}">
   <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -3167,16 +3612,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I2" s="14">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>68</v>
@@ -3196,16 +3641,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I3" s="14">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>68</v>
@@ -3225,16 +3670,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I4" s="14">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>68</v>
@@ -3254,16 +3699,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I5" s="14">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>68</v>
@@ -3283,16 +3728,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I6" s="14">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>68</v>
@@ -3312,16 +3757,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I7" s="14">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>68</v>
@@ -3341,16 +3786,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I8" s="14">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>68</v>
@@ -3370,16 +3815,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="I9" s="14">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>68</v>
@@ -3399,16 +3844,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I10" s="14">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>68</v>
@@ -3428,16 +3873,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="I11" s="14">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>68</v>
@@ -3457,16 +3902,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="I12" s="14">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>68</v>
@@ -3486,16 +3931,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="I13" s="14">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>68</v>
@@ -3515,16 +3960,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="I14" s="14">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>68</v>
@@ -3544,16 +3989,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="I15" s="14">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>68</v>
@@ -3573,16 +4018,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="I16" s="14">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>68</v>
@@ -3602,16 +4047,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="I17" s="14">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>68</v>
@@ -3631,16 +4076,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="I18" s="14">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>68</v>
@@ -3660,16 +4105,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="I19" s="14">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>68</v>
@@ -3689,16 +4134,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="I20" s="14">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>68</v>
@@ -3718,16 +4163,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I21" s="14">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="K21" s="15" t="s">
         <v>68</v>
@@ -3747,16 +4192,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I22" s="14">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="K22" s="15" t="s">
         <v>68</v>
@@ -3776,16 +4221,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I23" s="14">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="K23" s="15" t="s">
         <v>68</v>
@@ -3805,16 +4250,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I24" s="14">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="K24" s="15" t="s">
         <v>68</v>
@@ -3834,16 +4279,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I25" s="14">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="K25" s="15" t="s">
         <v>68</v>
@@ -3863,16 +4308,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I26" s="14">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="K26" s="15" t="s">
         <v>68</v>
@@ -3892,16 +4337,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I27" s="14">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="K27" s="15" t="s">
         <v>68</v>
@@ -3921,16 +4366,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I28" s="14">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="K28" s="15" t="s">
         <v>68</v>
@@ -3950,16 +4395,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I29" s="14">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="K29" s="15" t="s">
         <v>68</v>
@@ -3979,16 +4424,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I30" s="14">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="K30" s="15" t="s">
         <v>68</v>
@@ -4008,16 +4453,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I31" s="14">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="K31" s="15" t="s">
         <v>68</v>
@@ -4037,16 +4482,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I32" s="14">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="K32" s="15" t="s">
         <v>68</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D2822A8-766E-4111-828E-B44A5316BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{377FF916-09BF-4CFC-AA97-E35D66D9D92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
     <sheet name="Cocteles" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="Bebidas" sheetId="2" r:id="rId4"/>
+    <sheet name="Bebidas" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="256">
   <si>
     <t>No</t>
   </si>
@@ -730,93 +729,6 @@
     <t>images/menu/non-alcohol/25-soda-obush.jpg</t>
   </si>
   <si>
-    <t>Producto</t>
-  </si>
-  <si>
-    <t>Precio</t>
-  </si>
-  <si>
-    <t>Margarita</t>
-  </si>
-  <si>
-    <t>Tequila Sunrise</t>
-  </si>
-  <si>
-    <t>Orgasmo</t>
-  </si>
-  <si>
-    <t>Cuba Libre</t>
-  </si>
-  <si>
-    <t>El Padrino</t>
-  </si>
-  <si>
-    <t>Piña Colada</t>
-  </si>
-  <si>
-    <t>Gin Tonic</t>
-  </si>
-  <si>
-    <t>Dry Martini</t>
-  </si>
-  <si>
-    <t>Passion Fresh</t>
-  </si>
-  <si>
-    <t>Hawaiian Blue</t>
-  </si>
-  <si>
-    <t>Ton Collis</t>
-  </si>
-  <si>
-    <t>Rouse Apple</t>
-  </si>
-  <si>
-    <t>Bulls Cantina</t>
-  </si>
-  <si>
-    <t>Rumba Zafari</t>
-  </si>
-  <si>
-    <t>Mains Zafiro</t>
-  </si>
-  <si>
-    <t>Long Islad</t>
-  </si>
-  <si>
-    <t>Mojito Fresd</t>
-  </si>
-  <si>
-    <t>Blue Lagoon Drop</t>
-  </si>
-  <si>
-    <t>Soda Obush</t>
-  </si>
-  <si>
-    <t>Michelada Premium Frutal</t>
-  </si>
-  <si>
-    <t>Michelada Frutal</t>
-  </si>
-  <si>
-    <t>Michelada Premium Clásica</t>
-  </si>
-  <si>
-    <t>Michelada Clásica</t>
-  </si>
-  <si>
-    <t>Michelada Sin Alcohol Frutal</t>
-  </si>
-  <si>
-    <t>Michelada Sin Alcohol Clásica</t>
-  </si>
-  <si>
-    <t>Michelada Ginger Ale Frutal</t>
-  </si>
-  <si>
-    <t>Michelada Ginger Ale</t>
-  </si>
-  <si>
     <t>Poker</t>
   </si>
   <si>
@@ -1022,7 +934,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1085,14 +997,6 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1129,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1188,7 +1092,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -2303,7 +2206,7 @@
       <c r="H2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="24">
         <v>22000</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -2342,7 +2245,7 @@
       <c r="H3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="24">
         <v>20000</v>
       </c>
       <c r="J3" s="5" t="s">
@@ -2381,7 +2284,7 @@
       <c r="H4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="24">
         <v>22000</v>
       </c>
       <c r="J4" s="5" t="s">
@@ -2420,7 +2323,7 @@
       <c r="H5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="24">
         <v>18000</v>
       </c>
       <c r="J5" s="5" t="s">
@@ -2459,7 +2362,7 @@
       <c r="H6" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>20000</v>
       </c>
       <c r="J6" s="5" t="s">
@@ -2498,7 +2401,7 @@
       <c r="H7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="24">
         <v>22000</v>
       </c>
       <c r="J7" s="5" t="s">
@@ -2537,7 +2440,7 @@
       <c r="H8" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="24">
         <v>22000</v>
       </c>
       <c r="J8" s="5" t="s">
@@ -2576,7 +2479,7 @@
       <c r="H9" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="24">
         <v>22000</v>
       </c>
       <c r="J9" s="5" t="s">
@@ -2615,7 +2518,7 @@
       <c r="H10" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="24">
         <v>20000</v>
       </c>
       <c r="J10" s="5" t="s">
@@ -2654,7 +2557,7 @@
       <c r="H11" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="24">
         <v>20000</v>
       </c>
       <c r="J11" s="5" t="s">
@@ -2693,7 +2596,7 @@
       <c r="H12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="24">
         <v>20000</v>
       </c>
       <c r="J12" s="5" t="s">
@@ -2732,7 +2635,7 @@
       <c r="H13" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="25">
         <v>20000</v>
       </c>
       <c r="J13" s="5" t="s">
@@ -2771,7 +2674,7 @@
       <c r="H14" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="24">
         <v>22000</v>
       </c>
       <c r="J14" s="5" t="s">
@@ -2810,7 +2713,7 @@
       <c r="H15" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="24">
         <v>20000</v>
       </c>
       <c r="J15" s="5" t="s">
@@ -2849,7 +2752,7 @@
       <c r="H16" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="24">
         <v>22000</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -2888,7 +2791,7 @@
       <c r="H17" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>22000</v>
       </c>
       <c r="J17" s="5" t="s">
@@ -2927,7 +2830,7 @@
       <c r="H18" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="24">
         <v>20000</v>
       </c>
       <c r="J18" s="5" t="s">
@@ -2966,7 +2869,7 @@
       <c r="H19" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="24">
         <v>22000</v>
       </c>
       <c r="J19" s="5" t="s">
@@ -3005,7 +2908,7 @@
       <c r="H20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="24">
         <v>22000</v>
       </c>
       <c r="J20" s="5" t="s">
@@ -3044,7 +2947,7 @@
       <c r="H21" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="24">
         <v>25000</v>
       </c>
       <c r="J21" s="5" t="s">
@@ -3083,7 +2986,7 @@
       <c r="H22" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="25">
         <v>21000</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -3122,7 +3025,7 @@
       <c r="H23" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="24">
         <v>15000</v>
       </c>
       <c r="J23" s="5" t="s">
@@ -3161,7 +3064,7 @@
       <c r="H24" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="24">
         <v>15000</v>
       </c>
       <c r="J24" s="5" t="s">
@@ -3200,7 +3103,7 @@
       <c r="H25" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="24">
         <v>15000</v>
       </c>
       <c r="J25" s="5" t="s">
@@ -3239,7 +3142,7 @@
       <c r="H26" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="24">
         <v>13000</v>
       </c>
       <c r="J26" s="5" t="s">
@@ -3265,283 +3168,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BCC74E-788A-40B0-B92B-C30392239841}">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B3">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B4">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B7">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B9">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B10">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>200</v>
-      </c>
-      <c r="B14">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>201</v>
-      </c>
-      <c r="B15">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B16">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B18">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B19">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>204</v>
-      </c>
-      <c r="B20">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>205</v>
-      </c>
-      <c r="B21">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>206</v>
-      </c>
-      <c r="B22">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>207</v>
-      </c>
-      <c r="B23">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B24">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>209</v>
-      </c>
-      <c r="B25">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>210</v>
-      </c>
-      <c r="B26">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>211</v>
-      </c>
-      <c r="B27">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>212</v>
-      </c>
-      <c r="B28">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>215</v>
-      </c>
-      <c r="B31">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>216</v>
-      </c>
-      <c r="B32">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>217</v>
-      </c>
-      <c r="B33">
-        <v>14000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A989889E-D529-4390-8F71-069CF2800907}">
   <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -3612,16 +3238,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I2" s="14">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>68</v>
@@ -3641,16 +3267,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I3" s="14">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>68</v>
@@ -3670,16 +3296,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I4" s="14">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>68</v>
@@ -3699,16 +3325,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I5" s="14">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>68</v>
@@ -3728,16 +3354,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I6" s="14">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>68</v>
@@ -3757,16 +3383,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I7" s="14">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>68</v>
@@ -3786,16 +3412,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I8" s="14">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>68</v>
@@ -3815,16 +3441,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="I9" s="14">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>68</v>
@@ -3844,16 +3470,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="I10" s="14">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>68</v>
@@ -3873,16 +3499,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="I11" s="14">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>68</v>
@@ -3902,16 +3528,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="I12" s="14">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>68</v>
@@ -3931,16 +3557,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="I13" s="14">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>68</v>
@@ -3960,16 +3586,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="I14" s="14">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>68</v>
@@ -3989,16 +3615,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="I15" s="14">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>68</v>
@@ -4018,16 +3644,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="I16" s="14">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>68</v>
@@ -4047,16 +3673,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="I17" s="14">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>68</v>
@@ -4076,16 +3702,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="I18" s="14">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>68</v>
@@ -4105,16 +3731,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="I19" s="14">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>68</v>
@@ -4134,16 +3760,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="I20" s="14">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>68</v>
@@ -4163,16 +3789,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I21" s="14">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="K21" s="15" t="s">
         <v>68</v>
@@ -4192,16 +3818,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I22" s="14">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="K22" s="15" t="s">
         <v>68</v>
@@ -4221,16 +3847,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I23" s="14">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="K23" s="15" t="s">
         <v>68</v>
@@ -4250,16 +3876,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I24" s="14">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="K24" s="15" t="s">
         <v>68</v>
@@ -4279,16 +3905,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I25" s="14">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="K25" s="15" t="s">
         <v>68</v>
@@ -4308,16 +3934,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I26" s="14">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="K26" s="15" t="s">
         <v>68</v>
@@ -4337,16 +3963,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I27" s="14">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="K27" s="15" t="s">
         <v>68</v>
@@ -4366,16 +3992,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I28" s="14">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="K28" s="15" t="s">
         <v>68</v>
@@ -4395,16 +4021,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I29" s="14">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="K29" s="15" t="s">
         <v>68</v>
@@ -4424,16 +4050,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I30" s="14">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="K30" s="15" t="s">
         <v>68</v>
@@ -4453,16 +4079,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I31" s="14">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="K31" s="15" t="s">
         <v>68</v>
@@ -4482,16 +4108,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="I32" s="14">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="K32" s="15" t="s">
         <v>68</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{377FF916-09BF-4CFC-AA97-E35D66D9D92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EB5933C-D29C-4CF1-BF1B-B6D378249A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t>Nachos Zafiro</t>
   </si>
   <si>
-    <t>Totopos, carne desmechada, cheddar fundido, pico de gallo, guacamole y crema agria.</t>
+    <t>Totopos, carne desmechada, doble queso fundido, pico de gallo, guacamole y crema agria.</t>
   </si>
   <si>
     <t>Para compartir</t>
@@ -122,7 +122,7 @@
     <t>Choripan Argentino</t>
   </si>
   <si>
-    <t>Pan baggete crujiente, chorizo en forma de mariposa, acompañado de salsa de cilantro con perejil y papas rusticas con paprikka.</t>
+    <t>Pan baggete crujiente, chorizo en forma de mariposa, acompañado de salsa de cilantro con perejil y papas francesas.</t>
   </si>
   <si>
     <t>Sanduches y perros</t>
@@ -131,7 +131,7 @@
     <t>Perrito Loco</t>
   </si>
   <si>
-    <t>Salchicha americana, acompañado de guacamole, queso crema, queso cheddar, y tocineta en laminas.</t>
+    <t>Salchicha americana, acompañado de guacamole, queso crema, doble queso, y tocineta en laminas.</t>
   </si>
   <si>
     <t>Reina Pepiada</t>
@@ -161,13 +161,13 @@
     <t>Desgranado El Recucitador</t>
   </si>
   <si>
-    <t>Base de lechuga, papas rusticas, con pollo y carne desmechada, chorizo, tocineta y maiz tierno.</t>
+    <t>Base de lechuga, papas francesas, con pollo y carne desmechada, chorizo, tocineta y maiz tierno.</t>
   </si>
   <si>
     <t>Hamburguesa de la Casa</t>
   </si>
   <si>
-    <t>Pan artesanal, carne de 150gr, cebolla encurtida, tocineta dulce, queso cheddar, lechuaga, tomate y salsa de la casa.</t>
+    <t>Pan artesanal, carne de 150gr, cebolla caramelizada, tocineta dulce, doble queso, lechuaga, tomate y salsa de la casa.</t>
   </si>
   <si>
     <t>Hamburguesas</t>
@@ -1413,7 +1413,7 @@
   <cols>
     <col min="1" max="1" width="5" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="183.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="184" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -1780,10 +1780,10 @@
         <v>26000</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
@@ -2004,10 +2004,10 @@
         <v>17000</v>
       </c>
       <c r="K18" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15" t="s">
         <v>18</v>
@@ -2068,10 +2068,10 @@
         <v>17000</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15" t="s">
         <v>18</v>
@@ -2100,10 +2100,10 @@
         <v>17000</v>
       </c>
       <c r="K21" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>18</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EB5933C-D29C-4CF1-BF1B-B6D378249A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5427366-C85B-4C02-85D9-018D4B2FE5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <t>Orden</t>
   </si>
   <si>
-    <t>Tortilla Carne Zafiro</t>
+    <t>Tortilla Zafiro</t>
   </si>
   <si>
     <t>Tortilla rellena de queso fundiddo, carne o pollo desmechada y aguacate con ahogao.</t>
@@ -1033,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1092,8 +1092,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2206,7 +2205,7 @@
       <c r="H2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="15">
         <v>22000</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -2245,7 +2244,7 @@
       <c r="H3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="15">
         <v>20000</v>
       </c>
       <c r="J3" s="5" t="s">
@@ -2284,7 +2283,7 @@
       <c r="H4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="15">
         <v>22000</v>
       </c>
       <c r="J4" s="5" t="s">
@@ -2323,7 +2322,7 @@
       <c r="H5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="15">
         <v>18000</v>
       </c>
       <c r="J5" s="5" t="s">
@@ -2362,7 +2361,7 @@
       <c r="H6" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="15">
         <v>20000</v>
       </c>
       <c r="J6" s="5" t="s">
@@ -2401,7 +2400,7 @@
       <c r="H7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="15">
         <v>22000</v>
       </c>
       <c r="J7" s="5" t="s">
@@ -2440,7 +2439,7 @@
       <c r="H8" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="15">
         <v>22000</v>
       </c>
       <c r="J8" s="5" t="s">
@@ -2479,7 +2478,7 @@
       <c r="H9" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="15">
         <v>22000</v>
       </c>
       <c r="J9" s="5" t="s">
@@ -2518,7 +2517,7 @@
       <c r="H10" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="15">
         <v>20000</v>
       </c>
       <c r="J10" s="5" t="s">
@@ -2557,7 +2556,7 @@
       <c r="H11" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="15">
         <v>20000</v>
       </c>
       <c r="J11" s="5" t="s">
@@ -2596,7 +2595,7 @@
       <c r="H12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="15">
         <v>20000</v>
       </c>
       <c r="J12" s="5" t="s">
@@ -2635,7 +2634,7 @@
       <c r="H13" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <v>20000</v>
       </c>
       <c r="J13" s="5" t="s">
@@ -2674,7 +2673,7 @@
       <c r="H14" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="15">
         <v>22000</v>
       </c>
       <c r="J14" s="5" t="s">
@@ -2713,7 +2712,7 @@
       <c r="H15" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="15">
         <v>20000</v>
       </c>
       <c r="J15" s="5" t="s">
@@ -2752,7 +2751,7 @@
       <c r="H16" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="15">
         <v>22000</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -2791,7 +2790,7 @@
       <c r="H17" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="15">
         <v>22000</v>
       </c>
       <c r="J17" s="5" t="s">
@@ -2830,7 +2829,7 @@
       <c r="H18" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="15">
         <v>20000</v>
       </c>
       <c r="J18" s="5" t="s">
@@ -2869,7 +2868,7 @@
       <c r="H19" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="15">
         <v>22000</v>
       </c>
       <c r="J19" s="5" t="s">
@@ -2908,7 +2907,7 @@
       <c r="H20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="15">
         <v>22000</v>
       </c>
       <c r="J20" s="5" t="s">
@@ -2947,7 +2946,7 @@
       <c r="H21" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="15">
         <v>25000</v>
       </c>
       <c r="J21" s="5" t="s">
@@ -2986,7 +2985,7 @@
       <c r="H22" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="24">
         <v>21000</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -3025,7 +3024,7 @@
       <c r="H23" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="15">
         <v>15000</v>
       </c>
       <c r="J23" s="5" t="s">
@@ -3064,7 +3063,7 @@
       <c r="H24" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="15">
         <v>15000</v>
       </c>
       <c r="J24" s="5" t="s">
@@ -3103,7 +3102,7 @@
       <c r="H25" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="15">
         <v>15000</v>
       </c>
       <c r="J25" s="5" t="s">
@@ -3142,7 +3141,7 @@
       <c r="H26" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="15">
         <v>13000</v>
       </c>
       <c r="J26" s="5" t="s">

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5427366-C85B-4C02-85D9-018D4B2FE5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2510A7EA-2B90-474A-8AE3-99F5100E9407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
     <sheet name="Cocteles" sheetId="3" r:id="rId2"/>
     <sheet name="Bebidas" sheetId="2" r:id="rId3"/>
+    <sheet name="Micheladas" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="286">
   <si>
     <t>No</t>
   </si>
@@ -929,12 +930,102 @@
   <si>
     <t>images/menu/bebidas/don-julio-blanco.jpg</t>
   </si>
+  <si>
+    <t>Michelada Premium Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con Corona o Smirnoff Ice, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Corona o Smirnoff Ice, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$21.000</t>
+  </si>
+  <si>
+    <t>Michelada Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con cerveza nacional, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Cerveza nacional, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$18.000</t>
+  </si>
+  <si>
+    <t>Michelada Premium Clásica</t>
+  </si>
+  <si>
+    <t>Preparada con Corona o Smirnoff Ice, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Corona o Smirnoff Ice, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Michelada Clásica</t>
+  </si>
+  <si>
+    <t>Preparada con cerveza nacional, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Cerveza nacional, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$14.000</t>
+  </si>
+  <si>
+    <t>Michelada Sin Alcohol Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con soda o Bretaña, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Soda o Bretaña, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$15.000</t>
+  </si>
+  <si>
+    <t>Michelada Sin Alcohol Clásica</t>
+  </si>
+  <si>
+    <t>Preparada con soda o Bretaña, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Soda o Bretaña, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$13.000</t>
+  </si>
+  <si>
+    <t>Michelada Ginger Ale Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con Canada Dry, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Canada Dry, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$16.000</t>
+  </si>
+  <si>
+    <t>Michelada Ginger Ale</t>
+  </si>
+  <si>
+    <t>Preparada con Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -997,13 +1088,37 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FBFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1033,7 +1148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1093,6 +1208,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4134,4 +4258,452 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E85C11-7A7E-4D8D-BD07-645FEB554987}">
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultColWidth="56.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="18">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="30.75">
+      <c r="A2" s="26">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="26">
+        <v>1</v>
+      </c>
+      <c r="O2" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="30.75">
+      <c r="A3" s="26">
+        <v>2</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="26">
+        <v>2</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="30.75">
+      <c r="A4" s="26">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="26">
+        <v>3</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30.75">
+      <c r="A5" s="26">
+        <v>4</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="26">
+        <v>4</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="30.75">
+      <c r="A6" s="27">
+        <v>5</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="27">
+        <v>5</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="30.75">
+      <c r="A7" s="27">
+        <v>6</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="27">
+        <v>6</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="30.75">
+      <c r="A8" s="27">
+        <v>7</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="27">
+        <v>7</v>
+      </c>
+      <c r="O8" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="30.75">
+      <c r="A9" s="27">
+        <v>8</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="27">
+        <v>8</v>
+      </c>
+      <c r="O9" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2510A7EA-2B90-474A-8AE3-99F5100E9407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AED8243C-ADA1-43AC-914C-1BEC5FF8D4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
     <sheet name="Cocteles" sheetId="3" r:id="rId2"/>
     <sheet name="Bebidas" sheetId="2" r:id="rId3"/>
     <sheet name="Micheladas" sheetId="4" r:id="rId4"/>
+    <sheet name="Jugos y Limonadas" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="309">
   <si>
     <t>No</t>
   </si>
@@ -1019,6 +1020,75 @@
   </si>
   <si>
     <t>Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Jugo de Fresa en Agua</t>
+  </si>
+  <si>
+    <t>Jugos en agua</t>
+  </si>
+  <si>
+    <t>Jugo de Guanábana en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Lulo en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Mango en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Arazá en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Maracuyá en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Mora en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Fresa en Leche</t>
+  </si>
+  <si>
+    <t>Jugos en leche</t>
+  </si>
+  <si>
+    <t>Jugo de Guanábana en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Lulo en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Mango en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Arazá en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Maracuyá en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Mora en Leche</t>
+  </si>
+  <si>
+    <t>Limonada de Cereza</t>
+  </si>
+  <si>
+    <t>Limonadas</t>
+  </si>
+  <si>
+    <t>Limonada de Coco</t>
+  </si>
+  <si>
+    <t>Limonada de Lychee</t>
+  </si>
+  <si>
+    <t>Limonada de Mango Biche</t>
+  </si>
+  <si>
+    <t>Limonada de Sandía</t>
+  </si>
+  <si>
+    <t>Limonada de Hierbabuena</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1217,6 +1287,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4706,4 +4777,701 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6F544C-8D81-4F75-B1BC-E2A05AFA8EE5}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="28">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="28">
+        <v>2</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="28">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="28">
+        <v>4</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="28">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="28">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="28">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="28">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28">
+        <v>9000</v>
+      </c>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="28">
+        <v>9</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28">
+        <v>9000</v>
+      </c>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="28">
+        <v>10</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28">
+        <v>9000</v>
+      </c>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="28">
+        <v>11</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28">
+        <v>9000</v>
+      </c>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="28">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="28">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28">
+        <v>9000</v>
+      </c>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="28">
+        <v>13</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28">
+        <v>9000</v>
+      </c>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="28">
+        <v>14</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28">
+        <v>9000</v>
+      </c>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="28">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="28">
+        <v>15</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="28">
+        <v>16</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M17" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="28">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="28">
+        <v>18</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M19" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="28">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="28">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="28">
+        <v>20</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="28">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AED8243C-ADA1-43AC-914C-1BEC5FF8D4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{572BF6D0-6639-4B8B-9963-EFB26B44800F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
-    <sheet name="Cocteles" sheetId="3" r:id="rId2"/>
-    <sheet name="Bebidas" sheetId="2" r:id="rId3"/>
-    <sheet name="Micheladas" sheetId="4" r:id="rId4"/>
-    <sheet name="Jugos y Limonadas" sheetId="5" r:id="rId5"/>
+    <sheet name="Micheladas" sheetId="4" r:id="rId2"/>
+    <sheet name="Cocteles" sheetId="3" r:id="rId3"/>
+    <sheet name="Jugos y Limonadas" sheetId="5" r:id="rId4"/>
+    <sheet name="Bebidas" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -223,13 +223,109 @@
     <t> </t>
   </si>
   <si>
+    <t>Michelada Premium Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con Corona o Smirnoff Ice, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Con alcohol</t>
+  </si>
+  <si>
+    <t>Corona o Smirnoff Ice, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$21.000</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Michelada Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con cerveza nacional, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Cerveza nacional, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$18.000</t>
+  </si>
+  <si>
+    <t>Michelada Premium Clásica</t>
+  </si>
+  <si>
+    <t>Preparada con Corona o Smirnoff Ice, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Corona o Smirnoff Ice, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Michelada Clásica</t>
+  </si>
+  <si>
+    <t>Preparada con cerveza nacional, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Cerveza nacional, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$14.000</t>
+  </si>
+  <si>
+    <t>Michelada Sin Alcohol Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con soda o Bretaña, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Sin alcohol</t>
+  </si>
+  <si>
+    <t>Soda o Bretaña, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$15.000</t>
+  </si>
+  <si>
+    <t>Michelada Sin Alcohol Clásica</t>
+  </si>
+  <si>
+    <t>Preparada con soda o Bretaña, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Soda o Bretaña, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$13.000</t>
+  </si>
+  <si>
+    <t>Michelada Ginger Ale Frutal</t>
+  </si>
+  <si>
+    <t>Preparada con Canada Dry, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Canada Dry, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>$16.000</t>
+  </si>
+  <si>
+    <t>Michelada Ginger Ale</t>
+  </si>
+  <si>
+    <t>Preparada con Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
+    <t>Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
+  </si>
+  <si>
     <t>Margaritas </t>
   </si>
   <si>
     <t>Tequila, cítricos y licor de naranja en una mezcla fresca y vibrante, con borde escarchado y carácter clásico.</t>
-  </si>
-  <si>
-    <t>Con alcohol</t>
   </si>
   <si>
     <t xml:space="preserve">2 Oz Tequila Reposado 
@@ -244,9 +340,6 @@
   </si>
   <si>
     <t>images/menu/alcohol/01-margaritas-surtidas.jpeg</t>
-  </si>
-  <si>
-    <t>SI</t>
   </si>
   <si>
     <t>Coctel Tequila Sunrise </t>
@@ -636,9 +729,6 @@
     <t>Mezcla refrescante con soda, notas frutales y borde escarchado, pensada para una experiencia vibrante sin alcohol.</t>
   </si>
   <si>
-    <t>Sin alcohol</t>
-  </si>
-  <si>
     <t>Tradicional 
 360 Ml De Gaseosa Ginger. 
 360 Ml De Gaseosa Toronja (4)   
@@ -731,6 +821,75 @@
     <t>images/menu/non-alcohol/25-soda-obush.jpg</t>
   </si>
   <si>
+    <t>Jugo de Fresa en Agua</t>
+  </si>
+  <si>
+    <t>Jugos en agua</t>
+  </si>
+  <si>
+    <t>Jugo de Guanábana en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Lulo en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Mango en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Arazá en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Maracuyá en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Mora en Agua</t>
+  </si>
+  <si>
+    <t>Jugo de Fresa en Leche</t>
+  </si>
+  <si>
+    <t>Jugos en leche</t>
+  </si>
+  <si>
+    <t>Jugo de Guanábana en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Lulo en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Mango en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Arazá en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Maracuyá en Leche</t>
+  </si>
+  <si>
+    <t>Jugo de Mora en Leche</t>
+  </si>
+  <si>
+    <t>Limonada de Cereza</t>
+  </si>
+  <si>
+    <t>Limonadas</t>
+  </si>
+  <si>
+    <t>Limonada de Coco</t>
+  </si>
+  <si>
+    <t>Limonada de Lychee</t>
+  </si>
+  <si>
+    <t>Limonada de Mango Biche</t>
+  </si>
+  <si>
+    <t>Limonada de Sandía</t>
+  </si>
+  <si>
+    <t>Limonada de Hierbabuena</t>
+  </si>
+  <si>
     <t>Poker</t>
   </si>
   <si>
@@ -930,165 +1089,6 @@
   </si>
   <si>
     <t>images/menu/bebidas/don-julio-blanco.jpg</t>
-  </si>
-  <si>
-    <t>Michelada Premium Frutal</t>
-  </si>
-  <si>
-    <t>Preparada con Corona o Smirnoff Ice, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Corona o Smirnoff Ice, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>$21.000</t>
-  </si>
-  <si>
-    <t>Michelada Frutal</t>
-  </si>
-  <si>
-    <t>Preparada con cerveza nacional, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Cerveza nacional, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>$18.000</t>
-  </si>
-  <si>
-    <t>Michelada Premium Clásica</t>
-  </si>
-  <si>
-    <t>Preparada con Corona o Smirnoff Ice, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Corona o Smirnoff Ice, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Michelada Clásica</t>
-  </si>
-  <si>
-    <t>Preparada con cerveza nacional, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Cerveza nacional, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>$14.000</t>
-  </si>
-  <si>
-    <t>Michelada Sin Alcohol Frutal</t>
-  </si>
-  <si>
-    <t>Preparada con soda o Bretaña, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Soda o Bretaña, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>$15.000</t>
-  </si>
-  <si>
-    <t>Michelada Sin Alcohol Clásica</t>
-  </si>
-  <si>
-    <t>Preparada con soda o Bretaña, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Soda o Bretaña, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>$13.000</t>
-  </si>
-  <si>
-    <t>Michelada Ginger Ale Frutal</t>
-  </si>
-  <si>
-    <t>Preparada con Canada Dry, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Canada Dry, mezcla frutal, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>$16.000</t>
-  </si>
-  <si>
-    <t>Michelada Ginger Ale</t>
-  </si>
-  <si>
-    <t>Preparada con Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
-  </si>
-  <si>
-    <t>Jugo de Fresa en Agua</t>
-  </si>
-  <si>
-    <t>Jugos en agua</t>
-  </si>
-  <si>
-    <t>Jugo de Guanábana en Agua</t>
-  </si>
-  <si>
-    <t>Jugo de Lulo en Agua</t>
-  </si>
-  <si>
-    <t>Jugo de Mango en Agua</t>
-  </si>
-  <si>
-    <t>Jugo de Arazá en Agua</t>
-  </si>
-  <si>
-    <t>Jugo de Maracuyá en Agua</t>
-  </si>
-  <si>
-    <t>Jugo de Mora en Agua</t>
-  </si>
-  <si>
-    <t>Jugo de Fresa en Leche</t>
-  </si>
-  <si>
-    <t>Jugos en leche</t>
-  </si>
-  <si>
-    <t>Jugo de Guanábana en Leche</t>
-  </si>
-  <si>
-    <t>Jugo de Lulo en Leche</t>
-  </si>
-  <si>
-    <t>Jugo de Mango en Leche</t>
-  </si>
-  <si>
-    <t>Jugo de Arazá en Leche</t>
-  </si>
-  <si>
-    <t>Jugo de Maracuyá en Leche</t>
-  </si>
-  <si>
-    <t>Jugo de Mora en Leche</t>
-  </si>
-  <si>
-    <t>Limonada de Cereza</t>
-  </si>
-  <si>
-    <t>Limonadas</t>
-  </si>
-  <si>
-    <t>Limonada de Coco</t>
-  </si>
-  <si>
-    <t>Limonada de Lychee</t>
-  </si>
-  <si>
-    <t>Limonada de Mango Biche</t>
-  </si>
-  <si>
-    <t>Limonada de Sandía</t>
-  </si>
-  <si>
-    <t>Limonada de Hierbabuena</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1287,7 +1287,6 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2312,6 +2311,454 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E85C11-7A7E-4D8D-BD07-645FEB554987}">
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultColWidth="56.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="18">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="30.75">
+      <c r="A2" s="26">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="26">
+        <v>1</v>
+      </c>
+      <c r="O2" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="30.75">
+      <c r="A3" s="26">
+        <v>2</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="26">
+        <v>2</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="30.75">
+      <c r="A4" s="26">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="26">
+        <v>3</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30.75">
+      <c r="A5" s="26">
+        <v>4</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="26">
+        <v>4</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="30.75">
+      <c r="A6" s="27">
+        <v>5</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="27">
+        <v>5</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="30.75">
+      <c r="A7" s="27">
+        <v>6</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="27">
+        <v>6</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="30.75">
+      <c r="A8" s="27">
+        <v>7</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="27">
+        <v>7</v>
+      </c>
+      <c r="O8" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="30.75">
+      <c r="A9" s="27">
+        <v>8</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="27">
+        <v>8</v>
+      </c>
+      <c r="O9" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E651A84-53CF-42A2-A53F-F3F82D40C10B}">
   <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75"/>
@@ -2386,31 +2833,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="I2" s="15">
         <v>22000</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>18</v>
@@ -2425,25 +2872,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="I3" s="15">
         <v>20000</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K3" s="22" t="s">
         <v>18</v>
@@ -2464,25 +2911,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="I4" s="15">
         <v>22000</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="K4" s="22" t="s">
         <v>18</v>
@@ -2503,31 +2950,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="I5" s="15">
         <v>18000</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M5" s="22" t="s">
         <v>18</v>
@@ -2542,31 +2989,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="I6" s="15">
         <v>20000</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>18</v>
@@ -2581,25 +3028,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="I7" s="15">
         <v>22000</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="K7" s="22" t="s">
         <v>18</v>
@@ -2620,25 +3067,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="I8" s="15">
         <v>22000</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="K8" s="22" t="s">
         <v>18</v>
@@ -2659,31 +3106,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="I9" s="15">
         <v>22000</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M9" s="22" t="s">
         <v>18</v>
@@ -2698,31 +3145,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="I10" s="15">
         <v>20000</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M10" s="22" t="s">
         <v>18</v>
@@ -2737,25 +3184,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="I11" s="15">
         <v>20000</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>18</v>
@@ -2776,25 +3223,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="I12" s="15">
         <v>20000</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>18</v>
@@ -2815,31 +3262,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I13" s="24">
         <v>20000</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M13" s="22" t="s">
         <v>18</v>
@@ -2854,25 +3301,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="I14" s="15">
         <v>22000</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>18</v>
@@ -2893,25 +3340,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="I15" s="15">
         <v>20000</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>18</v>
@@ -2932,25 +3379,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="I16" s="15">
         <v>22000</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>18</v>
@@ -2971,25 +3418,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="I17" s="15">
         <v>22000</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>18</v>
@@ -3010,25 +3457,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="I18" s="15">
         <v>20000</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>18</v>
@@ -3049,25 +3496,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="I19" s="15">
         <v>22000</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>18</v>
@@ -3088,25 +3535,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="I20" s="15">
         <v>22000</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>18</v>
@@ -3127,31 +3574,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="I21" s="15">
         <v>25000</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M21" s="22" t="s">
         <v>18</v>
@@ -3166,31 +3613,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="I22" s="24">
         <v>21000</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M22" s="22" t="s">
         <v>18</v>
@@ -3205,25 +3652,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="I23" s="15">
         <v>15000</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="K23" s="22" t="s">
         <v>18</v>
@@ -3244,25 +3691,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="I24" s="15">
         <v>15000</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="K24" s="22" t="s">
         <v>18</v>
@@ -3283,25 +3730,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="I25" s="15">
         <v>15000</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="K25" s="22" t="s">
         <v>18</v>
@@ -3322,25 +3769,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="I26" s="15">
         <v>13000</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="K26" s="22" t="s">
         <v>18</v>
@@ -3361,7 +3808,704 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6F544C-8D81-4F75-B1BC-E2A05AFA8EE5}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="15">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="15">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="15">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="15">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="15">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15">
+        <v>9000</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="15">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15">
+        <v>9000</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15">
+        <v>9000</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="15">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15">
+        <v>9000</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="15">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15">
+        <v>9000</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="15">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15">
+        <v>9000</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15">
+        <v>9000</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="15">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="15">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="15">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="15">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="15">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="15">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15">
+        <v>8000</v>
+      </c>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="15">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A989889E-D529-4390-8F71-069CF2800907}">
   <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -3432,22 +4576,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I2" s="14">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>18</v>
@@ -3461,22 +4605,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I3" s="14">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>18</v>
@@ -3490,22 +4634,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>194</v>
+        <v>247</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I4" s="14">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>18</v>
@@ -3519,22 +4663,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I5" s="14">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>18</v>
@@ -3548,22 +4692,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I6" s="14">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>199</v>
+        <v>252</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M6" s="15" t="s">
         <v>18</v>
@@ -3577,22 +4721,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I7" s="14">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>18</v>
@@ -3606,22 +4750,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I8" s="14">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>203</v>
+        <v>256</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M8" s="15" t="s">
         <v>18</v>
@@ -3635,22 +4779,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="I9" s="14">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>18</v>
@@ -3664,22 +4808,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="I10" s="14">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>18</v>
@@ -3693,22 +4837,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="I11" s="14">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
@@ -3722,22 +4866,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="I12" s="14">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>214</v>
+        <v>267</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M12" s="15" t="s">
         <v>18</v>
@@ -3751,22 +4895,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="I13" s="14">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>18</v>
@@ -3780,22 +4924,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>217</v>
+        <v>270</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="I14" s="14">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>218</v>
+        <v>271</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M14" s="15" t="s">
         <v>18</v>
@@ -3809,22 +4953,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>219</v>
+        <v>272</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="I15" s="14">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M15" s="15" t="s">
         <v>18</v>
@@ -3838,22 +4982,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="I16" s="14">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M16" s="15" t="s">
         <v>18</v>
@@ -3867,22 +5011,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="I17" s="14">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>18</v>
@@ -3896,22 +5040,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="I18" s="14">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>228</v>
+        <v>281</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M18" s="15" t="s">
         <v>18</v>
@@ -3925,22 +5069,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>229</v>
+        <v>282</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="I19" s="14">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>230</v>
+        <v>283</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>18</v>
@@ -3954,22 +5098,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>231</v>
+        <v>284</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>232</v>
+        <v>285</v>
       </c>
       <c r="I20" s="14">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M20" s="15" t="s">
         <v>18</v>
@@ -3983,22 +5127,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I21" s="14">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>18</v>
@@ -4012,22 +5156,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>237</v>
+        <v>290</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I22" s="14">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M22" s="15" t="s">
         <v>18</v>
@@ -4041,22 +5185,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>239</v>
+        <v>292</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I23" s="14">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>18</v>
@@ -4070,22 +5214,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>241</v>
+        <v>294</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I24" s="14">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M24" s="15" t="s">
         <v>18</v>
@@ -4099,22 +5243,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>242</v>
+        <v>295</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I25" s="14">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>18</v>
@@ -4128,22 +5272,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>244</v>
+        <v>297</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I26" s="14">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M26" s="15" t="s">
         <v>18</v>
@@ -4157,22 +5301,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I27" s="14">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>246</v>
+        <v>299</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>18</v>
@@ -4186,22 +5330,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I28" s="14">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M28" s="15" t="s">
         <v>18</v>
@@ -4215,22 +5359,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I29" s="14">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>250</v>
+        <v>303</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M29" s="15" t="s">
         <v>18</v>
@@ -4244,22 +5388,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I30" s="14">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M30" s="15" t="s">
         <v>18</v>
@@ -4273,22 +5417,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>253</v>
+        <v>306</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I31" s="14">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>18</v>
@@ -4302,1173 +5446,28 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="I32" s="14">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M32" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N32" s="15">
         <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E85C11-7A7E-4D8D-BD07-645FEB554987}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultColWidth="56.42578125" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="1.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="18">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="30.75">
-      <c r="A2" s="26">
-        <v>1</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="26">
-        <v>1</v>
-      </c>
-      <c r="O2" s="26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="30.75">
-      <c r="A3" s="26">
-        <v>2</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="26">
-        <v>2</v>
-      </c>
-      <c r="O3" s="26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="30.75">
-      <c r="A4" s="26">
-        <v>3</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="26">
-        <v>3</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="30.75">
-      <c r="A5" s="26">
-        <v>4</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="26">
-        <v>4</v>
-      </c>
-      <c r="O5" s="26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="30.75">
-      <c r="A6" s="27">
-        <v>5</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="H6" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="J6" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" s="27">
-        <v>5</v>
-      </c>
-      <c r="O6" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="30.75">
-      <c r="A7" s="27">
-        <v>6</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="J7" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="27">
-        <v>6</v>
-      </c>
-      <c r="O7" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="30.75">
-      <c r="A8" s="27">
-        <v>7</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>281</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>282</v>
-      </c>
-      <c r="J8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="27">
-        <v>7</v>
-      </c>
-      <c r="O8" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="30.75">
-      <c r="A9" s="27">
-        <v>8</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="J9" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="M9" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="27">
-        <v>8</v>
-      </c>
-      <c r="O9" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6F544C-8D81-4F75-B1BC-E2A05AFA8EE5}">
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="28">
-        <v>1</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>286</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M2" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="28">
-        <v>2</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>288</v>
-      </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="28">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="28">
-        <v>4</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="28">
-        <v>5</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="28">
-        <v>6</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>292</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M7" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="28">
-        <v>7</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="28">
-        <v>8</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28">
-        <v>9000</v>
-      </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L9" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M9" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="28">
-        <v>9</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28">
-        <v>9000</v>
-      </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L10" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="28">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="28">
-        <v>10</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28">
-        <v>9000</v>
-      </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M11" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="28">
-        <v>11</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28">
-        <v>9000</v>
-      </c>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M12" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" s="28">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="28">
-        <v>12</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28">
-        <v>9000</v>
-      </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M13" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="28">
-        <v>13</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28">
-        <v>9000</v>
-      </c>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L14" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M14" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" s="28">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="28">
-        <v>14</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28">
-        <v>9000</v>
-      </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L15" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M15" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="28">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="28">
-        <v>15</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>302</v>
-      </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L16" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M16" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" s="28">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="28">
-        <v>16</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>304</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L17" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M17" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="28">
-        <v>17</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L18" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M18" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" s="28">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="28">
-        <v>18</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L19" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M19" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="28">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="28">
-        <v>19</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M20" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="28">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="28">
-        <v>20</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="L21" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="M21" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" s="28">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{351F7C9C-323F-474A-B398-15D7DFF967F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39743782-8BE1-4761-9EC6-F7430402A9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="339">
   <si>
     <t>No</t>
   </si>
@@ -88,6 +88,9 @@
     <t>Entradas</t>
   </si>
   <si>
+    <t>images/menu/comida/01-quesadilla-zafiro.png</t>
+  </si>
+  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -100,12 +103,18 @@
     <t>Mini corn dogs crujientes, salsa BBQ, salsa de soya y ajonjolí tostado.</t>
   </si>
   <si>
+    <t>images/menu/comida/02-corn-dog-zafiro-bites.png</t>
+  </si>
+  <si>
     <t>Tostones Cartageneros</t>
   </si>
   <si>
     <t>Patacones con hogao, acompañado de carne desmechada criolla y aguacate laminado.</t>
   </si>
   <si>
+    <t>images/menu/comida/03-tostones-cartageneros.png</t>
+  </si>
+  <si>
     <t>Nachos Zafiro</t>
   </si>
   <si>
@@ -115,12 +124,18 @@
     <t>Para compartir</t>
   </si>
   <si>
+    <t>images/menu/comida/04-nachos-zafiro.png</t>
+  </si>
+  <si>
     <t>Huevos Hogaos</t>
   </si>
   <si>
     <t>Cacerola de huevos al horno con hogao, tostadas y brotes.</t>
   </si>
   <si>
+    <t>images/menu/comida/05-huevos-hogaos.png</t>
+  </si>
+  <si>
     <t>Choripan Argentino</t>
   </si>
   <si>
@@ -130,48 +145,72 @@
     <t>Sanduches y perros</t>
   </si>
   <si>
+    <t>images/menu/comida/06-choripan-argentino.png</t>
+  </si>
+  <si>
     <t>Perrito Loco</t>
   </si>
   <si>
     <t>Salchicha americana, acompañado de guacamole, crema agria, queso fundido y tocineta crispy.</t>
   </si>
   <si>
+    <t>images/menu/comida/07-perrito-loco.png</t>
+  </si>
+  <si>
     <t>Reina Pepiada</t>
   </si>
   <si>
     <t>Sándwich relleno con pollo cremoso, queso doble crema, cebolla en brunoise, aguacate laminado y salsa de cilantro.</t>
   </si>
   <si>
+    <t>images/menu/comida/08-reina-pepiada.png</t>
+  </si>
+  <si>
     <t>Pinchos de Papas Fundidas</t>
   </si>
   <si>
     <t>Papas a la francesa montadas en brocheta, queso gratinado, cebolla morada, pimentón y un toque de salsa.</t>
   </si>
   <si>
+    <t>images/menu/comida/09-pinchos-de-papas-fundidas.jpeg</t>
+  </si>
+  <si>
     <t>Bocados Costa Zafiro</t>
   </si>
   <si>
     <t>Totopos/tartaletas, base de guacamole, camarón salteado al limón y cilantro.</t>
   </si>
   <si>
+    <t>images/menu/comida/10-bocados-costa-zafiro.jpeg</t>
+  </si>
+  <si>
     <t>Tortilla Desmechada al Zafiro</t>
   </si>
   <si>
     <t>Dos tortillas rellenas con carne desmechada, queso fundido, hogao, lechuga y cilantro fresco.</t>
   </si>
   <si>
+    <t>images/menu/comida/11-tortilla-desmechada-al-zafiro.png</t>
+  </si>
+  <si>
     <t>Tortillas al Zafiro</t>
   </si>
   <si>
     <t>Dos tortillas rellenas de pollo cremoso, doble queso, mantequilla y finas hierbas.</t>
   </si>
   <si>
+    <t>images/menu/comida/12-tortillas-al-zafiro.png</t>
+  </si>
+  <si>
     <t>Desgranado El Resucitador</t>
   </si>
   <si>
     <t>Base de lechuga, con pollo y carne desmechada con hogao, chorizo, tocineta, maiz tierno, salsa de la casa y porción de papas a la francesas.</t>
   </si>
   <si>
+    <t>images/menu/comida/13-desgranado-el-resucitador.png</t>
+  </si>
+  <si>
     <t>Hamburguesa de la Casa</t>
   </si>
   <si>
@@ -181,30 +220,45 @@
     <t>Hamburguesas</t>
   </si>
   <si>
+    <t>images/menu/comida/14-hamburguesa-de-la-casa.jpeg</t>
+  </si>
+  <si>
     <t>La Reina Doble</t>
   </si>
   <si>
     <t>Pan artesanal, doble carne de 110gr, boble queso, doble tocineta, huevo frito, salsa de Ajo, lechuga y tomate frescos.</t>
   </si>
   <si>
+    <t>images/menu/comida/15-la-reina-doble.png</t>
+  </si>
+  <si>
     <t>La Diabla</t>
   </si>
   <si>
     <t>Pan artesanal, carne de 110gr, carne desmechada, queso crema, aguacate, tocineta, jalapeños, cebolla salteada, salsa chipotle, lechuga y tomate frescos.</t>
   </si>
   <si>
+    <t>images/menu/comida/16-la-diabla.png</t>
+  </si>
+  <si>
     <t>La Original</t>
   </si>
   <si>
     <t>Pan artesanal, carnde 110gr, tocineta, queso doble crema, chorizo, lechuga y tomate frescos.</t>
   </si>
   <si>
+    <t>images/menu/comida/17-la-original.png</t>
+  </si>
+  <si>
     <t>Papas Zafiro</t>
   </si>
   <si>
     <t>Papas a la francesa, queso cheddar fundido y tocineta crispy.</t>
   </si>
   <si>
+    <t>images/menu/comida/18-papas-zafiro.jpeg</t>
+  </si>
+  <si>
     <t>Papas a la francesa</t>
   </si>
   <si>
@@ -214,6 +268,9 @@
     <t>Adiciones</t>
   </si>
   <si>
+    <t>images/menu/comida/19-papas-a-la-francesa.jpeg</t>
+  </si>
+  <si>
     <t>Helado con Brownie</t>
   </si>
   <si>
@@ -223,22 +280,34 @@
     <t>Postres</t>
   </si>
   <si>
+    <t>images/menu/comida/20-helado-con-brownie.jpeg</t>
+  </si>
+  <si>
     <t>Creep Achocolatado</t>
   </si>
   <si>
     <t>Base de helado, con frutos rojos o amarillos, con nutella y salsa de chocolate.</t>
   </si>
   <si>
+    <t>images/menu/comida/21-creep-achocolatado.jpeg</t>
+  </si>
+  <si>
     <t>Brownie con Helado</t>
   </si>
   <si>
     <t>Brownie con una bola de helado, acompañado de salsa de chocolate, fresas y arandanos.</t>
   </si>
   <si>
+    <t>images/menu/comida/22-brownie-con-helado.jpeg</t>
+  </si>
+  <si>
     <t>Tostadas con Amor</t>
   </si>
   <si>
     <t>Pan tajado crujiente, con base de nutella, fresas, arandanos, melocoton y menta fresca.</t>
+  </si>
+  <si>
+    <t>images/menu/comida/23-tostadas-con-amor.jpeg</t>
   </si>
   <si>
     <t> </t>
@@ -1186,7 +1255,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1209,6 +1278,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F7F7"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1239,7 +1314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1314,6 +1389,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1635,14 +1725,14 @@
   <cols>
     <col min="1" max="1" width="5" style="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.7109375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="30" style="28" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="28" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="28" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" style="28" customWidth="1"/>
     <col min="9" max="9" width="17.140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.140625" style="28" customWidth="1"/>
     <col min="11" max="11" width="8" style="28" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.140625" style="28" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="28" bestFit="1" customWidth="1"/>
@@ -1694,259 +1784,283 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="36">
-      <c r="A2" s="25">
+    <row r="2" spans="1:14" s="33" customFormat="1" ht="71.25">
+      <c r="A2" s="30">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="31"/>
+      <c r="E2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="I2" s="27">
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="I2" s="32">
         <v>21000</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="J2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="29" t="s">
+      <c r="K2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="29">
+      <c r="L2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="25">
+    <row r="3" spans="1:14" s="33" customFormat="1" ht="71.25">
+      <c r="A3" s="30">
         <v>2</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="B3" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27" t="s">
+      <c r="C3" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="31"/>
+      <c r="E3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="I3" s="27">
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="I3" s="32">
         <v>18000</v>
       </c>
-      <c r="K3" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="29" t="s">
+      <c r="J3" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="29">
+      <c r="L3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="34">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="36">
-      <c r="A4" s="25">
+    <row r="4" spans="1:14" s="33" customFormat="1" ht="71.25">
+      <c r="A4" s="30">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27" t="s">
+      <c r="B4" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="I4" s="27">
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="I4" s="32">
         <v>20000</v>
       </c>
-      <c r="K4" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="29" t="s">
+      <c r="J4" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="29">
+      <c r="L4" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="34">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="36">
-      <c r="A5" s="25">
+    <row r="5" spans="1:14" s="33" customFormat="1" ht="36">
+      <c r="A5" s="30">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="I5" s="27">
+      <c r="B5" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="I5" s="32">
         <v>24000</v>
       </c>
-      <c r="K5" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="29" t="s">
+      <c r="J5" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="29">
+      <c r="L5" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="34">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="25">
+    <row r="6" spans="1:14" s="33" customFormat="1" ht="54">
+      <c r="A6" s="30">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27" t="s">
+      <c r="B6" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="I6" s="27">
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="I6" s="32">
         <v>15000</v>
       </c>
-      <c r="K6" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="29" t="s">
+      <c r="J6" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="29">
+      <c r="L6" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="34">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="36">
-      <c r="A7" s="25">
+    <row r="7" spans="1:14" s="33" customFormat="1" ht="107.25">
+      <c r="A7" s="30">
         <v>6</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="I7" s="27">
-        <v>20000</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="29" t="s">
+      <c r="B7" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="I7" s="32">
+        <v>21000</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N7" s="29">
+      <c r="L7" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="34">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="36">
-      <c r="A8" s="25">
+    <row r="8" spans="1:14" s="33" customFormat="1" ht="89.25">
+      <c r="A8" s="30">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="I8" s="27">
+      <c r="B8" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="I8" s="32">
         <v>19000</v>
       </c>
-      <c r="K8" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="29" t="s">
+      <c r="J8" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="29">
+      <c r="L8" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="34">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="36">
-      <c r="A9" s="25">
+    <row r="9" spans="1:14" s="33" customFormat="1" ht="107.25">
+      <c r="A9" s="30">
         <v>8</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="I9" s="27">
+      <c r="B9" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="I9" s="32">
         <v>21000</v>
       </c>
-      <c r="K9" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="29" t="s">
+      <c r="J9" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="29">
+      <c r="L9" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="34">
         <v>8</v>
       </c>
     </row>
@@ -1955,10 +2069,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="27" t="s">
@@ -1969,6 +2083,9 @@
       <c r="I10" s="27">
         <v>18000</v>
       </c>
+      <c r="J10" s="29" t="s">
+        <v>45</v>
+      </c>
       <c r="K10" s="27" t="s">
         <v>0</v>
       </c>
@@ -1976,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" s="29">
         <v>9</v>
@@ -1987,20 +2104,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="27" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
       <c r="I11" s="27">
         <v>26000</v>
       </c>
+      <c r="J11" s="29" t="s">
+        <v>48</v>
+      </c>
       <c r="K11" s="27" t="s">
         <v>0</v>
       </c>
@@ -2008,105 +2128,114 @@
         <v>0</v>
       </c>
       <c r="M11" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="36">
-      <c r="A12" s="25">
+    <row r="12" spans="1:14" s="33" customFormat="1" ht="89.25">
+      <c r="A12" s="30">
         <v>11</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="I12" s="27">
+      <c r="B12" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="I12" s="32">
         <v>23000</v>
       </c>
-      <c r="K12" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="29" t="s">
+      <c r="J12" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N12" s="29">
+      <c r="L12" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" s="34">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="36">
-      <c r="A13" s="25">
+    <row r="13" spans="1:14" s="33" customFormat="1" ht="71.25">
+      <c r="A13" s="30">
         <v>12</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="I13" s="27">
+      <c r="B13" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="I13" s="32">
         <v>23000</v>
       </c>
-      <c r="K13" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="29" t="s">
+      <c r="J13" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N13" s="29">
+      <c r="L13" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="34">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="54">
-      <c r="A14" s="25">
+    <row r="14" spans="1:14" s="33" customFormat="1" ht="143.25">
+      <c r="A14" s="30">
         <v>13</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="I14" s="27">
+      <c r="B14" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="31"/>
+      <c r="E14" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="I14" s="32">
         <v>29000</v>
       </c>
-      <c r="K14" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14" s="29" t="s">
+      <c r="J14" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N14" s="29">
+      <c r="L14" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="34">
         <v>12</v>
       </c>
     </row>
@@ -2115,138 +2244,150 @@
         <v>14</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="27" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
       <c r="I15" s="27">
         <v>24000</v>
       </c>
+      <c r="J15" s="29" t="s">
+        <v>61</v>
+      </c>
       <c r="K15" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M15" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" s="29">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="36">
-      <c r="A16" s="25">
+    <row r="16" spans="1:14" s="33" customFormat="1" ht="107.25">
+      <c r="A16" s="30">
         <v>15</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="I16" s="27">
+      <c r="B16" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="31"/>
+      <c r="E16" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="I16" s="32">
         <v>28000</v>
       </c>
-      <c r="K16" s="27" t="s">
+      <c r="J16" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16" s="34">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="33" customFormat="1" ht="143.25">
+      <c r="A17" s="30">
+        <v>16</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="31"/>
+      <c r="E17" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="I17" s="32">
+        <v>28000</v>
+      </c>
+      <c r="J17" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" s="34">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="33" customFormat="1" ht="89.25">
+      <c r="A18" s="30">
         <v>17</v>
       </c>
-      <c r="L16" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M16" s="29" t="s">
+      <c r="B18" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="I18" s="32">
+        <v>24000</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N16" s="29">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="54">
-      <c r="A17" s="25">
+      <c r="L18" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" s="34">
         <v>16</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="I17" s="27">
-        <v>28000</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="29">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="36">
-      <c r="A18" s="25">
-        <v>17</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="I18" s="27">
-        <v>24000</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" s="29">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+    </row>
+    <row r="19" spans="1:14" ht="30.75">
       <c r="A19" s="25">
         <v>18</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="27" t="s">
@@ -2257,46 +2398,52 @@
       <c r="I19" s="27">
         <v>17000</v>
       </c>
+      <c r="J19" s="29" t="s">
+        <v>73</v>
+      </c>
       <c r="K19" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L19" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M19" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N19" s="29">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" ht="30.75">
       <c r="A20" s="25">
         <v>19</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="27" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
       <c r="I20" s="27">
         <v>7000</v>
       </c>
+      <c r="J20" s="29" t="s">
+        <v>77</v>
+      </c>
       <c r="K20" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L20" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M20" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" s="29">
         <v>18</v>
@@ -2307,20 +2454,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="27" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
       <c r="I21" s="27">
         <v>17000</v>
       </c>
+      <c r="J21" s="29" t="s">
+        <v>81</v>
+      </c>
       <c r="K21" s="27" t="s">
         <v>0</v>
       </c>
@@ -2328,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N21" s="29">
         <v>19</v>
@@ -2339,20 +2489,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="27" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F22" s="26"/>
       <c r="G22" s="26"/>
       <c r="I22" s="27">
         <v>19000</v>
       </c>
+      <c r="J22" s="29" t="s">
+        <v>84</v>
+      </c>
       <c r="K22" s="27" t="s">
         <v>0</v>
       </c>
@@ -2360,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22" s="29">
         <v>20</v>
@@ -2371,20 +2524,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="27" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
       <c r="I23" s="27">
         <v>17000</v>
       </c>
+      <c r="J23" s="29" t="s">
+        <v>87</v>
+      </c>
       <c r="K23" s="27" t="s">
         <v>0</v>
       </c>
@@ -2392,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N23" s="29">
         <v>21</v>
@@ -2403,20 +2559,23 @@
         <v>23</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="27" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
       <c r="I24" s="27">
         <v>17000</v>
       </c>
+      <c r="J24" s="29" t="s">
+        <v>90</v>
+      </c>
       <c r="K24" s="27" t="s">
         <v>0</v>
       </c>
@@ -2424,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N24" s="29">
         <v>22</v>
@@ -2499,7 +2658,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="30.75">
@@ -2507,46 +2666,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="21">
         <v>1</v>
       </c>
       <c r="O2" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30.75">
@@ -2554,46 +2713,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" s="21">
         <v>2</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30.75">
@@ -2601,46 +2760,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="21">
         <v>3</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="30.75">
@@ -2648,46 +2807,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="21">
         <v>4</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="30.75">
@@ -2695,46 +2854,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="22">
         <v>5</v>
       </c>
       <c r="O6" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="30.75">
@@ -2742,46 +2901,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>68</v>
-      </c>
       <c r="E7" s="22" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" s="22">
         <v>6</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="30.75">
@@ -2789,46 +2948,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="22">
         <v>7</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="30.75">
@@ -2836,46 +2995,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="22">
         <v>8</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2950,7 +3109,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="199.5">
@@ -2958,34 +3117,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="I2" s="11">
         <v>22000</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="17">
         <v>1</v>
@@ -2997,34 +3156,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="I3" s="11">
         <v>20000</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" s="17">
         <v>2</v>
@@ -3036,34 +3195,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="I4" s="11">
         <v>22000</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="17">
         <v>3</v>
@@ -3075,34 +3234,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="I5" s="11">
         <v>18000</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="17">
         <v>4</v>
@@ -3114,34 +3273,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="I6" s="11">
         <v>20000</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="17">
         <v>5</v>
@@ -3153,34 +3312,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="I7" s="11">
         <v>22000</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" s="17">
         <v>6</v>
@@ -3192,34 +3351,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I8" s="11">
         <v>22000</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="17">
         <v>7</v>
@@ -3231,34 +3390,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="I9" s="11">
         <v>22000</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="17">
         <v>8</v>
@@ -3270,34 +3429,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="I10" s="11">
         <v>20000</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" s="17">
         <v>9</v>
@@ -3309,34 +3468,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="I11" s="11">
         <v>20000</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="17">
         <v>10</v>
@@ -3348,34 +3507,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="I12" s="11">
         <v>20000</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" s="17">
         <v>11</v>
@@ -3387,34 +3546,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="I13" s="19">
         <v>20000</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N13" s="17">
         <v>12</v>
@@ -3426,34 +3585,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="I14" s="11">
         <v>22000</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N14" s="17">
         <v>13</v>
@@ -3465,34 +3624,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="I15" s="11">
         <v>20000</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" s="17">
         <v>14</v>
@@ -3504,34 +3663,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C16" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="I16" s="11">
         <v>22000</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N16" s="17">
         <v>15</v>
@@ -3543,34 +3702,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="I17" s="11">
         <v>22000</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N17" s="17">
         <v>16</v>
@@ -3582,34 +3741,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="I18" s="11">
         <v>20000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N18" s="17">
         <v>17</v>
@@ -3621,34 +3780,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="I19" s="11">
         <v>22000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N19" s="17">
         <v>18</v>
@@ -3660,34 +3819,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="I20" s="11">
         <v>22000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" s="17">
         <v>19</v>
@@ -3699,34 +3858,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="I21" s="11">
         <v>25000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N21" s="17">
         <v>20</v>
@@ -3738,34 +3897,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="I22" s="19">
         <v>21000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22" s="17">
         <v>21</v>
@@ -3777,34 +3936,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="I23" s="11">
         <v>15000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N23" s="17">
         <v>22</v>
@@ -3816,34 +3975,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="I24" s="11">
         <v>15000</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L24" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N24" s="17">
         <v>23</v>
@@ -3855,34 +4014,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="I25" s="11">
         <v>15000</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L25" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N25" s="17">
         <v>24</v>
@@ -3894,34 +4053,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="I26" s="11">
         <v>13000</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N26" s="17">
         <v>25</v>
@@ -3990,12 +4149,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
@@ -4005,13 +4164,13 @@
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="11">
         <v>1</v>
@@ -4022,12 +4181,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
@@ -4037,13 +4196,13 @@
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" s="11">
         <v>2</v>
@@ -4054,12 +4213,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -4069,13 +4228,13 @@
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="11">
         <v>3</v>
@@ -4086,12 +4245,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -4101,13 +4260,13 @@
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="11">
         <v>4</v>
@@ -4118,12 +4277,12 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -4133,13 +4292,13 @@
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="11">
         <v>5</v>
@@ -4150,12 +4309,12 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -4165,13 +4324,13 @@
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" s="11">
         <v>6</v>
@@ -4182,12 +4341,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -4197,13 +4356,13 @@
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="11">
         <v>7</v>
@@ -4214,12 +4373,12 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -4229,13 +4388,13 @@
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="11">
         <v>8</v>
@@ -4246,12 +4405,12 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -4261,13 +4420,13 @@
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" s="11">
         <v>9</v>
@@ -4278,12 +4437,12 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -4293,13 +4452,13 @@
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="11">
         <v>10</v>
@@ -4310,12 +4469,12 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
@@ -4325,13 +4484,13 @@
       </c>
       <c r="J12" s="11"/>
       <c r="K12" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" s="11">
         <v>11</v>
@@ -4342,12 +4501,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -4357,13 +4516,13 @@
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N13" s="11">
         <v>12</v>
@@ -4374,12 +4533,12 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
@@ -4389,13 +4548,13 @@
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N14" s="11">
         <v>13</v>
@@ -4406,12 +4565,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -4421,13 +4580,13 @@
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" s="11">
         <v>14</v>
@@ -4438,12 +4597,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -4453,13 +4612,13 @@
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N16" s="11">
         <v>15</v>
@@ -4470,12 +4629,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
@@ -4485,13 +4644,13 @@
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N17" s="11">
         <v>16</v>
@@ -4502,12 +4661,12 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -4517,13 +4676,13 @@
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N18" s="11">
         <v>17</v>
@@ -4534,12 +4693,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -4549,13 +4708,13 @@
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N19" s="11">
         <v>18</v>
@@ -4566,12 +4725,12 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
@@ -4581,13 +4740,13 @@
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" s="11">
         <v>19</v>
@@ -4598,12 +4757,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
@@ -4613,13 +4772,13 @@
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N21" s="11">
         <v>20</v>
@@ -4701,25 +4860,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I2" s="10">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="11">
         <v>1</v>
@@ -4730,25 +4889,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I3" s="10">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" s="11">
         <v>2</v>
@@ -4759,25 +4918,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I4" s="10">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="11">
         <v>3</v>
@@ -4788,25 +4947,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I5" s="10">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="11">
         <v>4</v>
@@ -4817,25 +4976,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I6" s="10">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="11">
         <v>5</v>
@@ -4846,25 +5005,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I7" s="10">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" s="11">
         <v>6</v>
@@ -4875,25 +5034,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I8" s="10">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="11">
         <v>7</v>
@@ -4904,25 +5063,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="I9" s="10">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="11">
         <v>8</v>
@@ -4933,25 +5092,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I10" s="10">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" s="11">
         <v>9</v>
@@ -4962,25 +5121,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="I11" s="10">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="11">
         <v>10</v>
@@ -4991,25 +5150,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="I12" s="10">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" s="11">
         <v>11</v>
@@ -5020,25 +5179,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="I13" s="10">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N13" s="11">
         <v>12</v>
@@ -5049,25 +5208,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="I14" s="10">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N14" s="11">
         <v>13</v>
@@ -5078,25 +5237,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="I15" s="10">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" s="11">
         <v>14</v>
@@ -5107,25 +5266,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="I16" s="10">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N16" s="11">
         <v>15</v>
@@ -5136,25 +5295,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="I17" s="10">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N17" s="11">
         <v>16</v>
@@ -5165,25 +5324,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="I18" s="10">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N18" s="11">
         <v>17</v>
@@ -5194,25 +5353,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="I19" s="10">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N19" s="11">
         <v>18</v>
@@ -5223,25 +5382,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="I20" s="10">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" s="11">
         <v>19</v>
@@ -5252,25 +5411,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I21" s="10">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N21" s="11">
         <v>20</v>
@@ -5281,25 +5440,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I22" s="10">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22" s="11">
         <v>21</v>
@@ -5310,25 +5469,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I23" s="10">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N23" s="11">
         <v>22</v>
@@ -5339,25 +5498,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I24" s="10">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N24" s="11">
         <v>23</v>
@@ -5368,25 +5527,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I25" s="10">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N25" s="11">
         <v>24</v>
@@ -5397,25 +5556,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I26" s="10">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N26" s="11">
         <v>25</v>
@@ -5426,25 +5585,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I27" s="10">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N27" s="11">
         <v>26</v>
@@ -5455,25 +5614,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I28" s="10">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N28" s="11">
         <v>27</v>
@@ -5484,25 +5643,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I29" s="10">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N29" s="11">
         <v>28</v>
@@ -5513,25 +5672,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I30" s="10">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N30" s="11">
         <v>29</v>
@@ -5542,25 +5701,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I31" s="10">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" s="11">
         <v>30</v>
@@ -5571,25 +5730,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="I32" s="10">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N32" s="11">
         <v>31</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39743782-8BE1-4761-9EC6-F7430402A9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD3EA607-3307-4967-88AF-E14911C68A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="342">
   <si>
     <t>No</t>
   </si>
@@ -328,6 +328,9 @@
     <t>$21.000</t>
   </si>
   <si>
+    <t>images/menu/alcohol/21-micheladas-surtidas.jpeg</t>
+  </si>
+  <si>
     <t>SI</t>
   </si>
   <si>
@@ -341,6 +344,9 @@
   </si>
   <si>
     <t>$18.000</t>
+  </si>
+  <si>
+    <t>images/menu/non-alcohol/27-michelada-cerveza-importada-corona.jpeg</t>
   </si>
   <si>
     <t>Michelada Premium Clásica</t>
@@ -975,6 +981,9 @@
   </si>
   <si>
     <t>Limonada de Sandía</t>
+  </si>
+  <si>
+    <t>/images/menu/jugos/limonada-de-sandia.jpeg</t>
   </si>
   <si>
     <t>Limonada de Hierbabuena</t>
@@ -2601,6 +2610,7 @@
   <cols>
     <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -2661,7 +2671,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30.75">
+    <row r="2" spans="1:15" ht="60.75">
       <c r="A2" s="21">
         <v>1</v>
       </c>
@@ -2689,14 +2699,14 @@
       <c r="I2" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="21" t="s">
-        <v>91</v>
+      <c r="J2" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M2" s="21" t="s">
         <v>19</v>
@@ -2708,15 +2718,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="30.75">
+    <row r="3" spans="1:15" ht="60.75">
       <c r="A3" s="21">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>91</v>
@@ -2728,22 +2738,22 @@
         <v>91</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>91</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>91</v>
+        <v>102</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>19</v>
@@ -2755,15 +2765,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="30.75">
+    <row r="4" spans="1:15" ht="45.75">
       <c r="A4" s="21">
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>91</v>
@@ -2775,22 +2785,22 @@
         <v>91</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>91</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>91</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" s="21" t="s">
         <v>19</v>
@@ -2802,15 +2812,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30.75">
+    <row r="5" spans="1:15" ht="45.75">
       <c r="A5" s="21">
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>91</v>
@@ -2822,22 +2832,22 @@
         <v>91</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>91</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>91</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M5" s="21" t="s">
         <v>19</v>
@@ -2849,42 +2859,42 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30.75">
+    <row r="6" spans="1:15" ht="60.75">
       <c r="A6" s="22">
         <v>5</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>91</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>91</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>91</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>91</v>
+        <v>115</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>19</v>
@@ -2896,42 +2906,42 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="30.75">
+    <row r="7" spans="1:15" ht="45.75">
       <c r="A7" s="22">
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>91</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>91</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H7" s="22" t="s">
         <v>91</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J7" s="22" t="s">
         <v>91</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>19</v>
@@ -2943,42 +2953,42 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="30.75">
+    <row r="8" spans="1:15" ht="45.75">
       <c r="A8" s="22">
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>91</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>91</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>91</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J8" s="22" t="s">
         <v>91</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M8" s="22" t="s">
         <v>19</v>
@@ -2990,42 +3000,42 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="30.75">
+    <row r="9" spans="1:15" ht="45.75">
       <c r="A9" s="22">
         <v>8</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>91</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>91</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H9" s="22" t="s">
         <v>91</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J9" s="22" t="s">
         <v>91</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" s="22" t="s">
         <v>19</v>
@@ -3117,31 +3127,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I2" s="11">
         <v>22000</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M2" s="17" t="s">
         <v>19</v>
@@ -3156,25 +3166,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I3" s="11">
         <v>20000</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>19</v>
@@ -3195,25 +3205,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I4" s="11">
         <v>22000</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K4" s="17" t="s">
         <v>19</v>
@@ -3234,31 +3244,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I5" s="11">
         <v>18000</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M5" s="17" t="s">
         <v>19</v>
@@ -3273,31 +3283,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I6" s="11">
         <v>20000</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M6" s="17" t="s">
         <v>19</v>
@@ -3312,25 +3322,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I7" s="11">
         <v>22000</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K7" s="17" t="s">
         <v>19</v>
@@ -3351,25 +3361,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I8" s="11">
         <v>22000</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>19</v>
@@ -3390,31 +3400,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I9" s="11">
         <v>22000</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" s="17" t="s">
         <v>19</v>
@@ -3429,31 +3439,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I10" s="11">
         <v>20000</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M10" s="17" t="s">
         <v>19</v>
@@ -3468,25 +3478,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I11" s="11">
         <v>20000</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>19</v>
@@ -3507,25 +3517,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I12" s="11">
         <v>20000</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K12" s="17" t="s">
         <v>19</v>
@@ -3546,31 +3556,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I13" s="19">
         <v>20000</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M13" s="17" t="s">
         <v>19</v>
@@ -3585,25 +3595,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I14" s="11">
         <v>22000</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>19</v>
@@ -3624,25 +3634,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I15" s="11">
         <v>20000</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K15" s="17" t="s">
         <v>19</v>
@@ -3663,25 +3673,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I16" s="11">
         <v>22000</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K16" s="17" t="s">
         <v>19</v>
@@ -3702,25 +3712,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I17" s="11">
         <v>22000</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K17" s="17" t="s">
         <v>19</v>
@@ -3741,25 +3751,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I18" s="11">
         <v>20000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K18" s="17" t="s">
         <v>19</v>
@@ -3780,25 +3790,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I19" s="11">
         <v>22000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K19" s="17" t="s">
         <v>19</v>
@@ -3819,25 +3829,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I20" s="11">
         <v>22000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K20" s="17" t="s">
         <v>19</v>
@@ -3858,31 +3868,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I21" s="11">
         <v>25000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M21" s="17" t="s">
         <v>19</v>
@@ -3897,31 +3907,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I22" s="19">
         <v>21000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>97</v>
+        <v>231</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="M22" s="17" t="s">
         <v>19</v>
@@ -3936,25 +3946,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I23" s="11">
         <v>15000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>19</v>
@@ -3975,25 +3985,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I24" s="11">
         <v>15000</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K24" s="17" t="s">
         <v>19</v>
@@ -4014,25 +4024,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I25" s="11">
         <v>15000</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K25" s="17" t="s">
         <v>19</v>
@@ -4053,25 +4063,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I26" s="11">
         <v>13000</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K26" s="17" t="s">
         <v>19</v>
@@ -4149,12 +4159,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
@@ -4164,10 +4174,10 @@
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>19</v>
@@ -4181,12 +4191,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
@@ -4196,10 +4206,10 @@
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>19</v>
@@ -4213,12 +4223,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -4228,10 +4238,10 @@
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>19</v>
@@ -4245,12 +4255,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -4260,10 +4270,10 @@
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>19</v>
@@ -4277,12 +4287,12 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -4292,10 +4302,10 @@
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>19</v>
@@ -4309,12 +4319,12 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -4324,10 +4334,10 @@
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>19</v>
@@ -4341,12 +4351,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -4356,10 +4366,10 @@
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>19</v>
@@ -4373,12 +4383,12 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -4388,10 +4398,10 @@
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>19</v>
@@ -4405,12 +4415,12 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -4420,10 +4430,10 @@
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>19</v>
@@ -4437,12 +4447,12 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -4452,10 +4462,10 @@
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>19</v>
@@ -4469,12 +4479,12 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
@@ -4484,10 +4494,10 @@
       </c>
       <c r="J12" s="11"/>
       <c r="K12" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>19</v>
@@ -4501,12 +4511,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -4516,10 +4526,10 @@
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>19</v>
@@ -4533,12 +4543,12 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
@@ -4548,10 +4558,10 @@
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>19</v>
@@ -4565,12 +4575,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -4580,10 +4590,10 @@
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>19</v>
@@ -4597,12 +4607,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -4612,10 +4622,10 @@
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>19</v>
@@ -4629,12 +4639,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
@@ -4644,10 +4654,10 @@
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>19</v>
@@ -4661,12 +4671,12 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -4676,10 +4686,10 @@
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>19</v>
@@ -4693,12 +4703,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -4708,10 +4718,10 @@
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>19</v>
@@ -4725,12 +4735,12 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
@@ -4738,12 +4748,14 @@
       <c r="I20" s="11">
         <v>10000</v>
       </c>
-      <c r="J20" s="11"/>
+      <c r="J20" s="11" t="s">
+        <v>273</v>
+      </c>
       <c r="K20" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>19</v>
@@ -4757,12 +4769,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
@@ -4772,10 +4784,10 @@
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>19</v>
@@ -4860,22 +4872,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I2" s="10">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>19</v>
@@ -4889,22 +4901,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I3" s="10">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>19</v>
@@ -4918,22 +4930,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I4" s="10">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>19</v>
@@ -4947,22 +4959,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I5" s="10">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>19</v>
@@ -4976,22 +4988,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I6" s="10">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>19</v>
@@ -5005,22 +5017,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I7" s="10">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>19</v>
@@ -5034,22 +5046,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I8" s="10">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>19</v>
@@ -5063,22 +5075,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I9" s="10">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>19</v>
@@ -5092,22 +5104,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I10" s="10">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>19</v>
@@ -5121,22 +5133,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I11" s="10">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>19</v>
@@ -5150,22 +5162,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I12" s="10">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>19</v>
@@ -5179,22 +5191,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I13" s="10">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>19</v>
@@ -5208,22 +5220,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I14" s="10">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>19</v>
@@ -5237,22 +5249,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I15" s="10">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>19</v>
@@ -5266,22 +5278,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I16" s="10">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>19</v>
@@ -5295,22 +5307,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I17" s="10">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>19</v>
@@ -5324,22 +5336,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I18" s="10">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>19</v>
@@ -5353,22 +5365,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I19" s="10">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>19</v>
@@ -5382,22 +5394,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I20" s="10">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>19</v>
@@ -5411,22 +5423,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I21" s="10">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>19</v>
@@ -5440,22 +5452,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I22" s="10">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>19</v>
@@ -5469,22 +5481,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I23" s="10">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>19</v>
@@ -5498,22 +5510,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I24" s="10">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M24" s="11" t="s">
         <v>19</v>
@@ -5527,22 +5539,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I25" s="10">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>19</v>
@@ -5556,22 +5568,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I26" s="10">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>19</v>
@@ -5585,22 +5597,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I27" s="10">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M27" s="11" t="s">
         <v>19</v>
@@ -5614,22 +5626,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I28" s="10">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>19</v>
@@ -5643,22 +5655,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I29" s="10">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M29" s="11" t="s">
         <v>19</v>
@@ -5672,22 +5684,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I30" s="10">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M30" s="11" t="s">
         <v>19</v>
@@ -5701,22 +5713,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I31" s="10">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M31" s="11" t="s">
         <v>19</v>
@@ -5730,22 +5742,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I32" s="10">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M32" s="11" t="s">
         <v>19</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD3EA607-3307-4967-88AF-E14911C68A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFFCB2A7-4E8E-4B34-9293-C52DBE99F1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
     <t>Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
   </si>
   <si>
-    <t>Margaritas </t>
+    <t>Margaritas ssssssssssssssssss</t>
   </si>
   <si>
     <t>Tequila, cítricos y licor de naranja en una mezcla fresca y vibrante, con borde escarchado y carácter clásico.</t>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFFCB2A7-4E8E-4B34-9293-C52DBE99F1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B465A7F-6B08-45F7-B74F-2CCCF5DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,7 +418,7 @@
     <t>Canada Dry, zumo de limón, hielo, escarchado y tajada de limón.</t>
   </si>
   <si>
-    <t>Margaritas ssssssssssssssssss</t>
+    <t>Margaritas</t>
   </si>
   <si>
     <t>Tequila, cítricos y licor de naranja en una mezcla fresca y vibrante, con borde escarchado y carácter clásico.</t>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B465A7F-6B08-45F7-B74F-2CCCF5DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CA6F65-C0CB-4BB4-9442-F0F3E1967F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="347">
   <si>
     <t>No</t>
   </si>
@@ -220,7 +220,7 @@
     <t>Hamburguesas</t>
   </si>
   <si>
-    <t>images/menu/comida/14-hamburguesa-de-la-casa.jpeg</t>
+    <t>images/menu/comida/14-hamburguesa-de-la-casa.png</t>
   </si>
   <si>
     <t>La Reina Doble</t>
@@ -987,6 +987,21 @@
   </si>
   <si>
     <t>Limonada de Hierbabuena</t>
+  </si>
+  <si>
+    <t>Soda Italiana de Maracuyá</t>
+  </si>
+  <si>
+    <t>Sodas italianas</t>
+  </si>
+  <si>
+    <t>/images/menu/jugos/soda-italiana-maracuya.png</t>
+  </si>
+  <si>
+    <t>Soda Italiana de Frutos Rojos</t>
+  </si>
+  <si>
+    <t>/images/menu/jugos/soda-italiana-frutos-rojos.png</t>
   </si>
   <si>
     <t>Poker</t>
@@ -2248,38 +2263,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="36">
-      <c r="A15" s="25">
+    <row r="15" spans="1:14" s="33" customFormat="1" ht="107.25">
+      <c r="A15" s="30">
         <v>14</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="31"/>
+      <c r="E15" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="I15" s="27">
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="I15" s="32">
         <v>24000</v>
       </c>
-      <c r="J15" s="29" t="s">
+      <c r="J15" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="K15" s="27" t="s">
+      <c r="K15" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="L15" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="M15" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="N15" s="29">
+      <c r="M15" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="34">
         <v>13</v>
       </c>
     </row>
@@ -4104,7 +4119,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6F544C-8D81-4F75-B1BC-E2A05AFA8EE5}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
@@ -4794,6 +4809,74 @@
       </c>
       <c r="N21" s="11">
         <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11">
+        <v>13000</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" s="11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11">
+        <v>13000</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N23" s="11">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4872,16 +4955,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I2" s="10">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K2" s="11" t="s">
         <v>98</v>
@@ -4901,16 +4984,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I3" s="10">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K3" s="11" t="s">
         <v>98</v>
@@ -4930,16 +5013,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I4" s="10">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>98</v>
@@ -4959,22 +5042,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I5" s="10">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>19</v>
@@ -4988,16 +5071,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I6" s="10">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>98</v>
@@ -5017,16 +5100,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I7" s="10">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>98</v>
@@ -5046,16 +5129,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I8" s="10">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>98</v>
@@ -5075,16 +5158,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I9" s="10">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>98</v>
@@ -5104,22 +5187,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I10" s="10">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>19</v>
@@ -5133,16 +5216,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I11" s="10">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>98</v>
@@ -5162,16 +5245,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I12" s="10">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>98</v>
@@ -5191,16 +5274,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I13" s="10">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>98</v>
@@ -5220,16 +5303,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I14" s="10">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>98</v>
@@ -5249,16 +5332,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I15" s="10">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>98</v>
@@ -5278,16 +5361,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="I16" s="10">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>98</v>
@@ -5307,16 +5390,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I17" s="10">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>98</v>
@@ -5336,16 +5419,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="I18" s="10">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>98</v>
@@ -5365,16 +5448,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I19" s="10">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>98</v>
@@ -5394,16 +5477,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="I20" s="10">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>98</v>
@@ -5423,16 +5506,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I21" s="10">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>98</v>
@@ -5452,16 +5535,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I22" s="10">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>98</v>
@@ -5481,16 +5564,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I23" s="10">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>98</v>
@@ -5510,16 +5593,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I24" s="10">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>98</v>
@@ -5539,16 +5622,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I25" s="10">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>98</v>
@@ -5568,16 +5651,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I26" s="10">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>98</v>
@@ -5597,16 +5680,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I27" s="10">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>98</v>
@@ -5626,16 +5709,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I28" s="10">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>98</v>
@@ -5655,16 +5738,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I29" s="10">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>98</v>
@@ -5684,16 +5767,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I30" s="10">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>98</v>
@@ -5713,16 +5796,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I31" s="10">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>98</v>
@@ -5742,16 +5825,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I32" s="10">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>98</v>

--- a/data/ZafiroMenu.xlsx
+++ b/data/ZafiroMenu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CA6F65-C0CB-4BB4-9442-F0F3E1967F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25699FDA-C666-4FB9-A173-4C6A351656D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comida" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="350">
   <si>
     <t>No</t>
   </si>
@@ -308,6 +308,15 @@
   </si>
   <si>
     <t>images/menu/comida/23-tostadas-con-amor.jpeg</t>
+  </si>
+  <si>
+    <t>Papas Corte Zafiro</t>
+  </si>
+  <si>
+    <t>Papas a la francesa, salchicha artesanal, tocineta glaseada crujiente sobre base de lechuga fresca. Acompañado de nuestras salsas de la casa.</t>
+  </si>
+  <si>
+    <t>images/menu/comida/24-papas-corte-zafiro.jpeg</t>
   </si>
   <si>
     <t> </t>
@@ -1744,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" style="25" bestFit="1" customWidth="1"/>
@@ -1764,7 +1773,7 @@
     <col min="15" max="16384" width="9.140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="25" customFormat="1">
+    <row r="1" spans="1:14" s="25" customFormat="1" ht="71.25">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1913,7 +1922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="33" customFormat="1" ht="36">
+    <row r="5" spans="1:14" s="33" customFormat="1" ht="89.25">
       <c r="A5" s="30">
         <v>4</v>
       </c>
@@ -2088,7 +2097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="36">
+    <row r="10" spans="1:14" ht="107.25">
       <c r="A10" s="25">
         <v>9</v>
       </c>
@@ -2123,7 +2132,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="36">
+    <row r="11" spans="1:14" ht="71.25">
       <c r="A11" s="25">
         <v>10</v>
       </c>
@@ -2403,7 +2412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="30.75">
+    <row r="19" spans="1:14" ht="54">
       <c r="A19" s="25">
         <v>18</v>
       </c>
@@ -2426,10 +2435,10 @@
         <v>73</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L19" s="27" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M19" s="29" t="s">
         <v>19</v>
@@ -2438,7 +2447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="30.75">
+    <row r="20" spans="1:14" ht="36">
       <c r="A20" s="25">
         <v>19</v>
       </c>
@@ -2473,7 +2482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="36">
+    <row r="21" spans="1:14" ht="89.25">
       <c r="A21" s="25">
         <v>20</v>
       </c>
@@ -2508,7 +2517,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="36">
+    <row r="22" spans="1:14" ht="71.25">
       <c r="A22" s="25">
         <v>21</v>
       </c>
@@ -2543,7 +2552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="36">
+    <row r="23" spans="1:14" ht="89.25">
       <c r="A23" s="25">
         <v>22</v>
       </c>
@@ -2578,7 +2587,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="36">
+    <row r="24" spans="1:14" ht="89.25">
       <c r="A24" s="25">
         <v>23</v>
       </c>
@@ -2611,6 +2620,38 @@
       </c>
       <c r="N24" s="29">
         <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="143.25">
+      <c r="A25" s="25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="28">
+        <v>25000</v>
+      </c>
+      <c r="J25" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="K25" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="N25" s="28">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2683,7 +2724,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="60.75">
@@ -2691,37 +2732,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E2" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="G2" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M2" s="21" t="s">
         <v>19</v>
@@ -2730,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="60.75">
@@ -2738,37 +2779,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E3" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="G3" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>19</v>
@@ -2777,7 +2818,7 @@
         <v>2</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="45.75">
@@ -2785,37 +2826,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C4" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="21" t="s">
+      <c r="J4" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="K4" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M4" s="21" t="s">
         <v>19</v>
@@ -2824,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="45.75">
@@ -2832,37 +2873,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E5" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="G5" s="21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M5" s="21" t="s">
         <v>19</v>
@@ -2871,7 +2912,7 @@
         <v>4</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="60.75">
@@ -2879,37 +2920,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>19</v>
@@ -2918,7 +2959,7 @@
         <v>5</v>
       </c>
       <c r="O6" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="45.75">
@@ -2926,37 +2967,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>113</v>
-      </c>
       <c r="F7" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M7" s="22" t="s">
         <v>19</v>
@@ -2965,7 +3006,7 @@
         <v>6</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="45.75">
@@ -2973,37 +3014,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M8" s="22" t="s">
         <v>19</v>
@@ -3012,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="45.75">
@@ -3020,37 +3061,37 @@
         <v>8</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E9" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>110</v>
-      </c>
       <c r="J9" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M9" s="22" t="s">
         <v>19</v>
@@ -3059,7 +3100,7 @@
         <v>8</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3134,7 +3175,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="199.5">
@@ -3142,31 +3183,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I2" s="11">
         <v>22000</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M2" s="17" t="s">
         <v>19</v>
@@ -3181,25 +3222,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I3" s="11">
         <v>20000</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>19</v>
@@ -3220,25 +3261,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I4" s="11">
         <v>22000</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K4" s="17" t="s">
         <v>19</v>
@@ -3259,31 +3300,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I5" s="11">
         <v>18000</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M5" s="17" t="s">
         <v>19</v>
@@ -3298,31 +3339,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I6" s="11">
         <v>20000</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M6" s="17" t="s">
         <v>19</v>
@@ -3337,25 +3378,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I7" s="11">
         <v>22000</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K7" s="17" t="s">
         <v>19</v>
@@ -3376,25 +3417,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I8" s="11">
         <v>22000</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>19</v>
@@ -3415,31 +3456,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I9" s="11">
         <v>22000</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M9" s="17" t="s">
         <v>19</v>
@@ -3454,31 +3495,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I10" s="11">
         <v>20000</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M10" s="17" t="s">
         <v>19</v>
@@ -3493,25 +3534,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I11" s="11">
         <v>20000</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>19</v>
@@ -3532,25 +3573,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I12" s="11">
         <v>20000</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K12" s="17" t="s">
         <v>19</v>
@@ -3571,31 +3612,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I13" s="19">
         <v>20000</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M13" s="17" t="s">
         <v>19</v>
@@ -3610,25 +3651,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I14" s="11">
         <v>22000</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>19</v>
@@ -3649,25 +3690,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I15" s="11">
         <v>20000</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K15" s="17" t="s">
         <v>19</v>
@@ -3688,25 +3729,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I16" s="11">
         <v>22000</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K16" s="17" t="s">
         <v>19</v>
@@ -3727,25 +3768,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I17" s="11">
         <v>22000</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K17" s="17" t="s">
         <v>19</v>
@@ -3766,25 +3807,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I18" s="11">
         <v>20000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K18" s="17" t="s">
         <v>19</v>
@@ -3805,25 +3846,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I19" s="11">
         <v>22000</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K19" s="17" t="s">
         <v>19</v>
@@ -3844,25 +3885,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I20" s="11">
         <v>22000</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K20" s="17" t="s">
         <v>19</v>
@@ -3883,31 +3924,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I21" s="11">
         <v>25000</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M21" s="17" t="s">
         <v>19</v>
@@ -3922,25 +3963,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I22" s="19">
         <v>21000</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K22" s="17" t="s">
         <v>19</v>
@@ -3961,25 +4002,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I23" s="11">
         <v>15000</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>19</v>
@@ -4000,25 +4041,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I24" s="11">
         <v>15000</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K24" s="17" t="s">
         <v>19</v>
@@ -4039,25 +4080,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I25" s="11">
         <v>15000</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K25" s="17" t="s">
         <v>19</v>
@@ -4078,25 +4119,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I26" s="11">
         <v>13000</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K26" s="17" t="s">
         <v>19</v>
@@ -4174,12 +4215,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
@@ -4189,10 +4230,10 @@
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>19</v>
@@ -4206,12 +4247,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
@@ -4221,10 +4262,10 @@
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>19</v>
@@ -4238,12 +4279,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -4253,10 +4294,10 @@
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>19</v>
@@ -4270,12 +4311,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -4285,10 +4326,10 @@
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>19</v>
@@ -4302,12 +4343,12 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -4317,10 +4358,10 @@
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>19</v>
@@ -4334,12 +4375,12 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -4349,10 +4390,10 @@
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>19</v>
@@ -4366,12 +4407,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -4381,10 +4422,10 @@
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>19</v>
@@ -4398,12 +4439,12 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -4413,10 +4454,10 @@
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>19</v>
@@ -4430,12 +4471,12 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -4445,10 +4486,10 @@
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>19</v>
@@ -4462,12 +4503,12 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -4477,10 +4518,10 @@
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>19</v>
@@ -4494,12 +4535,12 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
@@ -4509,10 +4550,10 @@
       </c>
       <c r="J12" s="11"/>
       <c r="K12" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>19</v>
@@ -4526,12 +4567,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -4541,10 +4582,10 @@
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>19</v>
@@ -4558,12 +4599,12 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
@@ -4573,10 +4614,10 @@
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>19</v>
@@ -4590,12 +4631,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -4605,10 +4646,10 @@
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>19</v>
@@ -4622,12 +4663,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -4637,10 +4678,10 @@
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>19</v>
@@ -4654,12 +4695,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
@@ -4669,10 +4710,10 @@
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>19</v>
@@ -4686,12 +4727,12 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -4701,10 +4742,10 @@
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>19</v>
@@ -4718,12 +4759,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -4733,10 +4774,10 @@
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>19</v>
@@ -4750,12 +4791,12 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
@@ -4764,13 +4805,13 @@
         <v>10000</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>19</v>
@@ -4784,12 +4825,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
@@ -4799,10 +4840,10 @@
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>19</v>
@@ -4816,12 +4857,12 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
@@ -4830,13 +4871,13 @@
         <v>13000</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>19</v>
@@ -4850,12 +4891,12 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
@@ -4864,13 +4905,13 @@
         <v>13000</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>19</v>
@@ -4955,22 +4996,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I2" s="10">
         <v>5000</v>
       </c>
       <c r="J2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>19</v>
@@ -4984,22 +5025,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I3" s="10">
         <v>5000</v>
       </c>
       <c r="J3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>19</v>
@@ -5013,22 +5054,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I4" s="10">
         <v>9000</v>
       </c>
       <c r="J4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>19</v>
@@ -5042,16 +5083,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I5" s="10">
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>19</v>
@@ -5071,22 +5112,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I6" s="10">
         <v>8000</v>
       </c>
       <c r="J6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>19</v>
@@ -5100,22 +5141,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I7" s="10">
         <v>7000</v>
       </c>
       <c r="J7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>19</v>
@@ -5129,22 +5170,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I8" s="10">
         <v>5000</v>
       </c>
       <c r="J8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>19</v>
@@ -5158,22 +5199,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I9" s="10">
         <v>13000</v>
       </c>
       <c r="J9" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>19</v>
@@ -5187,16 +5228,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I10" s="10">
         <v>18000</v>
       </c>
       <c r="J10" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>19</v>
@@ -5216,22 +5257,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I11" s="10">
         <v>5000</v>
       </c>
       <c r="J11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>19</v>
@@ -5245,22 +5286,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I12" s="10">
         <v>3000</v>
       </c>
       <c r="J12" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>19</v>
@@ -5274,22 +5315,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I13" s="10">
         <v>4000</v>
       </c>
       <c r="J13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>19</v>
@@ -5303,22 +5344,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I14" s="10">
         <v>5000</v>
       </c>
       <c r="J14" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>19</v>
@@ -5332,22 +5373,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I15" s="10">
         <v>5000</v>
       </c>
       <c r="J15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>19</v>
@@ -5361,22 +5402,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I16" s="10">
         <v>5000</v>
       </c>
       <c r="J16" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>19</v>
@@ -5390,22 +5431,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I17" s="10">
         <v>5000</v>
       </c>
       <c r="J17" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>19</v>
@@ -5419,22 +5460,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I18" s="10">
         <v>5000</v>
       </c>
       <c r="J18" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>19</v>
@@ -5448,22 +5489,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I19" s="10">
         <v>5000</v>
       </c>
       <c r="J19" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>19</v>
@@ -5477,22 +5518,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="I20" s="10">
         <v>5000</v>
       </c>
       <c r="J20" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>19</v>
@@ -5506,22 +5547,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I21" s="10">
         <v>55000</v>
       </c>
       <c r="J21" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>19</v>
@@ -5535,22 +5576,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I22" s="10">
         <v>55000</v>
       </c>
       <c r="J22" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>19</v>
@@ -5564,22 +5605,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I23" s="10">
         <v>55000</v>
       </c>
       <c r="J23" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>19</v>
@@ -5593,22 +5634,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I24" s="10">
         <v>95000</v>
       </c>
       <c r="J24" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M24" s="11" t="s">
         <v>19</v>
@@ -5622,22 +5663,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I25" s="10">
         <v>90000</v>
       </c>
       <c r="J25" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>19</v>
@@ -5651,22 +5692,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I26" s="10">
         <v>55000</v>
       </c>
       <c r="J26" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>19</v>
@@ -5680,22 +5721,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I27" s="10">
         <v>250000</v>
       </c>
       <c r="J27" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M27" s="11" t="s">
         <v>19</v>
@@ -5709,22 +5750,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I28" s="10">
         <v>260000</v>
       </c>
       <c r="J28" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>19</v>
@@ -5738,22 +5779,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I29" s="10">
         <v>280000</v>
       </c>
       <c r="J29" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M29" s="11" t="s">
         <v>19</v>
@@ -5767,22 +5808,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I30" s="10">
         <v>80000</v>
       </c>
       <c r="J30" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M30" s="11" t="s">
         <v>19</v>
@@ -5796,22 +5837,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I31" s="10">
         <v>120000</v>
       </c>
       <c r="J31" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M31" s="11" t="s">
         <v>19</v>
@@ -5825,22 +5866,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I32" s="10">
         <v>380000</v>
       </c>
       <c r="J32" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M32" s="11" t="s">
         <v>19</v>
